--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Customer" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aging" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Trend" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="By Customer" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aging" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily Trend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,16 +24,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -142,246 +130,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -668,7 +416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -677,12 +425,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -730,12 +478,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -744,27 +491,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>open_shipments</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>total_outstanding</t>
         </is>
@@ -1117,12 +864,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1131,12 +877,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>aging_bucket</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
@@ -1184,12 +930,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1198,19 +943,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>collected</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="B2" t="n">
@@ -1218,7 +963,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="B3" t="n">
@@ -1226,7 +971,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B4" t="n">
@@ -1234,7 +979,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46137</v>
       </c>
       <c r="B5" t="n">
@@ -1242,7 +987,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46138</v>
       </c>
       <c r="B6" t="n">
@@ -1250,7 +995,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46139</v>
       </c>
       <c r="B7" t="n">
@@ -1258,7 +1003,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46140</v>
       </c>
       <c r="B8" t="n">
@@ -1266,7 +1011,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46141</v>
       </c>
       <c r="B9" t="n">
@@ -1274,7 +1019,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B10" t="n">
@@ -1282,7 +1027,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B11" t="n">
@@ -1290,7 +1035,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46144</v>
       </c>
       <c r="B12" t="n">
@@ -1298,7 +1043,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>46145</v>
       </c>
       <c r="B13" t="n">
@@ -1306,7 +1051,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>46146</v>
       </c>
       <c r="B14" t="n">
@@ -1314,7 +1059,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="B15" t="n">
@@ -1322,7 +1067,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="B16" t="n">
@@ -1330,7 +1075,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="B17" t="n">
@@ -1338,7 +1083,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B18" t="n">
@@ -1346,7 +1091,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>46151</v>
       </c>
       <c r="B19" t="n">
@@ -1354,7 +1099,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>46152</v>
       </c>
       <c r="B20" t="n">
@@ -1362,7 +1107,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="B21" t="n">
@@ -1370,7 +1115,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="B22" t="n">
@@ -1378,7 +1123,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="B23" t="n">
@@ -1386,7 +1131,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46156</v>
       </c>
       <c r="B24" t="n">
@@ -1394,7 +1139,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B25" t="n">
@@ -1402,7 +1147,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46158</v>
       </c>
       <c r="B26" t="n">
@@ -1410,7 +1155,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46159</v>
       </c>
       <c r="B27" t="n">
@@ -1418,7 +1163,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B28" t="n">
@@ -1426,7 +1171,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B29" t="n">
@@ -1434,7 +1179,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="B30" t="n">
@@ -1442,7 +1187,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B31" t="n">
@@ -1451,12 +1196,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1465,157 +1209,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>shipment_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>material_category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>material_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>quantity_mt</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>rate_per_mt</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sale_value_without_gst</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gst_rate_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gst_amount</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>invoice_amount</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>shipment_date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>delivered_date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>invoice_date</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>vehicle_number</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>sales_order_id</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>amount_paid_total</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>outstanding</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>is_settled</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>due_date_parsed</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>days_to_due</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>days_overdue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>eligible_for_reminder</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>eligible_for_overdue</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>in_7d_window</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>in_3d_window</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>in_1d_window</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>aging_bucket</t>
         </is>
@@ -1709,7 +1453,7 @@
       <c r="S2" t="b">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="U2" t="n">
@@ -1842,7 +1586,7 @@
       <c r="S3" t="b">
         <v>0</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="T3" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="U3" t="n">
@@ -1975,7 +1719,7 @@
       <c r="S4" t="b">
         <v>0</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="U4" t="n">
@@ -2108,7 +1852,7 @@
       <c r="S5" t="b">
         <v>0</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="U5" t="n">
@@ -2241,7 +1985,7 @@
       <c r="S6" t="b">
         <v>0</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="U6" t="n">
@@ -2374,7 +2118,7 @@
       <c r="S7" t="b">
         <v>0</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" s="1" t="n">
         <v>46137</v>
       </c>
       <c r="U7" t="n">
@@ -2507,7 +2251,7 @@
       <c r="S8" t="b">
         <v>0</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="U8" t="n">
@@ -2640,7 +2384,7 @@
       <c r="S9" t="b">
         <v>0</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="T9" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="U9" t="n">
@@ -2773,7 +2517,7 @@
       <c r="S10" t="b">
         <v>0</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="T10" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="U10" t="n">
@@ -2906,7 +2650,7 @@
       <c r="S11" t="b">
         <v>0</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="T11" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="U11" t="n">
@@ -3039,7 +2783,7 @@
       <c r="S12" t="b">
         <v>0</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="T12" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="U12" t="n">
@@ -3172,7 +2916,7 @@
       <c r="S13" t="b">
         <v>0</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="T13" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="U13" t="n">
@@ -3305,7 +3049,7 @@
       <c r="S14" t="b">
         <v>0</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="T14" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U14" t="n">
@@ -3438,7 +3182,7 @@
       <c r="S15" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="T15" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U15" t="n">
@@ -3571,7 +3315,7 @@
       <c r="S16" t="b">
         <v>0</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="T16" s="1" t="n">
         <v>46186</v>
       </c>
       <c r="U16" t="n">
@@ -3704,7 +3448,7 @@
       <c r="S17" t="b">
         <v>0</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="T17" s="1" t="n">
         <v>46187</v>
       </c>
       <c r="U17" t="n">
@@ -3837,7 +3581,7 @@
       <c r="S18" t="b">
         <v>0</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="T18" s="1" t="n">
         <v>46189</v>
       </c>
       <c r="U18" t="n">
@@ -3970,7 +3714,7 @@
       <c r="S19" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="T19" s="1" t="n">
         <v>46189</v>
       </c>
       <c r="U19" t="n">
@@ -4103,7 +3847,7 @@
       <c r="S20" t="b">
         <v>0</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="T20" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U20" t="n">
@@ -4236,7 +3980,7 @@
       <c r="S21" t="b">
         <v>0</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="T21" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U21" t="n">
@@ -4369,7 +4113,7 @@
       <c r="S22" t="b">
         <v>0</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="T22" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U22" t="n">
@@ -4502,7 +4246,7 @@
       <c r="S23" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="T23" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U23" t="n">
@@ -4635,7 +4379,7 @@
       <c r="S24" t="b">
         <v>0</v>
       </c>
-      <c r="T24" s="2" t="n">
+      <c r="T24" s="1" t="n">
         <v>46194</v>
       </c>
       <c r="U24" t="n">
@@ -4768,7 +4512,7 @@
       <c r="S25" t="b">
         <v>0</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="T25" s="1" t="n">
         <v>46195</v>
       </c>
       <c r="U25" t="n">
@@ -4901,7 +4645,7 @@
       <c r="S26" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="2" t="n">
+      <c r="T26" s="1" t="n">
         <v>46180</v>
       </c>
       <c r="U26" t="n">
@@ -5034,7 +4778,7 @@
       <c r="S27" t="b">
         <v>0</v>
       </c>
-      <c r="T27" s="2" t="n">
+      <c r="T27" s="1" t="n">
         <v>46196</v>
       </c>
       <c r="U27" t="n">
@@ -5167,7 +4911,7 @@
       <c r="S28" t="b">
         <v>0</v>
       </c>
-      <c r="T28" s="2" t="n">
+      <c r="T28" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="U28" t="n">
@@ -5300,7 +5044,7 @@
       <c r="S29" t="b">
         <v>0</v>
       </c>
-      <c r="T29" s="2" t="n">
+      <c r="T29" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="U29" t="n">
@@ -5433,7 +5177,7 @@
       <c r="S30" t="b">
         <v>0</v>
       </c>
-      <c r="T30" s="2" t="n">
+      <c r="T30" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="U30" t="n">
@@ -5566,7 +5310,7 @@
       <c r="S31" t="b">
         <v>0</v>
       </c>
-      <c r="T31" s="2" t="n">
+      <c r="T31" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="U31" t="n">
@@ -5699,7 +5443,7 @@
       <c r="S32" t="b">
         <v>0</v>
       </c>
-      <c r="T32" s="2" t="n">
+      <c r="T32" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U32" t="n">
@@ -5832,7 +5576,7 @@
       <c r="S33" t="b">
         <v>0</v>
       </c>
-      <c r="T33" s="2" t="n">
+      <c r="T33" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U33" t="n">
@@ -5965,7 +5709,7 @@
       <c r="S34" t="b">
         <v>0</v>
       </c>
-      <c r="T34" s="2" t="n">
+      <c r="T34" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U34" t="n">
@@ -6098,7 +5842,7 @@
       <c r="S35" t="b">
         <v>0</v>
       </c>
-      <c r="T35" s="2" t="n">
+      <c r="T35" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U35" t="n">
@@ -6231,7 +5975,7 @@
       <c r="S36" t="b">
         <v>0</v>
       </c>
-      <c r="T36" s="2" t="n">
+      <c r="T36" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U36" t="n">
@@ -6364,7 +6108,7 @@
       <c r="S37" t="b">
         <v>0</v>
       </c>
-      <c r="T37" s="2" t="n">
+      <c r="T37" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U37" t="n">
@@ -6497,7 +6241,7 @@
       <c r="S38" t="b">
         <v>0</v>
       </c>
-      <c r="T38" s="2" t="n">
+      <c r="T38" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U38" t="n">
@@ -6630,7 +6374,7 @@
       <c r="S39" t="b">
         <v>0</v>
       </c>
-      <c r="T39" s="2" t="n">
+      <c r="T39" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U39" t="n">
@@ -6763,7 +6507,7 @@
       <c r="S40" t="b">
         <v>0</v>
       </c>
-      <c r="T40" s="2" t="n">
+      <c r="T40" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U40" t="n">
@@ -6896,7 +6640,7 @@
       <c r="S41" t="b">
         <v>0</v>
       </c>
-      <c r="T41" s="2" t="n">
+      <c r="T41" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U41" t="n">
@@ -7029,7 +6773,7 @@
       <c r="S42" t="b">
         <v>0</v>
       </c>
-      <c r="T42" s="2" t="n">
+      <c r="T42" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U42" t="n">
@@ -7162,7 +6906,7 @@
       <c r="S43" t="b">
         <v>0</v>
       </c>
-      <c r="T43" s="2" t="n">
+      <c r="T43" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U43" t="n">
@@ -7295,7 +7039,7 @@
       <c r="S44" t="b">
         <v>0</v>
       </c>
-      <c r="T44" s="2" t="n">
+      <c r="T44" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U44" t="n">
@@ -7428,7 +7172,7 @@
       <c r="S45" t="b">
         <v>0</v>
       </c>
-      <c r="T45" s="2" t="n">
+      <c r="T45" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U45" t="n">
@@ -7561,7 +7305,7 @@
       <c r="S46" t="b">
         <v>0</v>
       </c>
-      <c r="T46" s="2" t="n">
+      <c r="T46" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U46" t="n">
@@ -7694,7 +7438,7 @@
       <c r="S47" t="b">
         <v>0</v>
       </c>
-      <c r="T47" s="2" t="n">
+      <c r="T47" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U47" t="n">
@@ -7827,7 +7571,7 @@
       <c r="S48" t="b">
         <v>0</v>
       </c>
-      <c r="T48" s="2" t="n">
+      <c r="T48" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U48" t="n">
@@ -7960,7 +7704,7 @@
       <c r="S49" t="b">
         <v>0</v>
       </c>
-      <c r="T49" s="2" t="n">
+      <c r="T49" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U49" t="n">
@@ -8093,7 +7837,7 @@
       <c r="S50" t="b">
         <v>0</v>
       </c>
-      <c r="T50" s="2" t="n">
+      <c r="T50" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U50" t="n">
@@ -8226,7 +7970,7 @@
       <c r="S51" t="b">
         <v>0</v>
       </c>
-      <c r="T51" s="2" t="n">
+      <c r="T51" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U51" t="n">
@@ -8359,7 +8103,7 @@
       <c r="S52" t="b">
         <v>0</v>
       </c>
-      <c r="T52" s="2" t="n">
+      <c r="T52" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U52" t="n">
@@ -8492,7 +8236,7 @@
       <c r="S53" t="b">
         <v>0</v>
       </c>
-      <c r="T53" s="2" t="n">
+      <c r="T53" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U53" t="n">
@@ -8625,7 +8369,7 @@
       <c r="S54" t="b">
         <v>0</v>
       </c>
-      <c r="T54" s="2" t="n">
+      <c r="T54" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U54" t="n">
@@ -8758,7 +8502,7 @@
       <c r="S55" t="b">
         <v>0</v>
       </c>
-      <c r="T55" s="2" t="n">
+      <c r="T55" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U55" t="n">
@@ -8891,7 +8635,7 @@
       <c r="S56" t="b">
         <v>0</v>
       </c>
-      <c r="T56" s="2" t="n">
+      <c r="T56" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U56" t="n">
@@ -9024,7 +8768,7 @@
       <c r="S57" t="b">
         <v>0</v>
       </c>
-      <c r="T57" s="2" t="n">
+      <c r="T57" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U57" t="n">
@@ -9157,7 +8901,7 @@
       <c r="S58" t="b">
         <v>0</v>
       </c>
-      <c r="T58" s="2" t="n">
+      <c r="T58" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U58" t="n">
@@ -9290,7 +9034,7 @@
       <c r="S59" t="b">
         <v>0</v>
       </c>
-      <c r="T59" s="2" t="n">
+      <c r="T59" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U59" t="n">
@@ -9423,7 +9167,7 @@
       <c r="S60" t="b">
         <v>0</v>
       </c>
-      <c r="T60" s="2" t="n">
+      <c r="T60" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U60" t="n">
@@ -9556,7 +9300,7 @@
       <c r="S61" t="b">
         <v>0</v>
       </c>
-      <c r="T61" s="2" t="n">
+      <c r="T61" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U61" t="n">
@@ -9689,7 +9433,7 @@
       <c r="S62" t="b">
         <v>0</v>
       </c>
-      <c r="T62" s="2" t="n">
+      <c r="T62" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U62" t="n">
@@ -9822,7 +9566,7 @@
       <c r="S63" t="b">
         <v>0</v>
       </c>
-      <c r="T63" s="2" t="n">
+      <c r="T63" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U63" t="n">
@@ -9955,7 +9699,7 @@
       <c r="S64" t="b">
         <v>0</v>
       </c>
-      <c r="T64" s="2" t="n">
+      <c r="T64" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U64" t="n">
@@ -10088,7 +9832,7 @@
       <c r="S65" t="b">
         <v>0</v>
       </c>
-      <c r="T65" s="2" t="n">
+      <c r="T65" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U65" t="n">
@@ -10221,7 +9965,7 @@
       <c r="S66" t="b">
         <v>0</v>
       </c>
-      <c r="T66" s="2" t="n">
+      <c r="T66" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U66" t="n">
@@ -10354,7 +10098,7 @@
       <c r="S67" t="b">
         <v>0</v>
       </c>
-      <c r="T67" s="2" t="n">
+      <c r="T67" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U67" t="n">
@@ -10487,7 +10231,7 @@
       <c r="S68" t="b">
         <v>0</v>
       </c>
-      <c r="T68" s="2" t="n">
+      <c r="T68" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U68" t="n">
@@ -10620,7 +10364,7 @@
       <c r="S69" t="b">
         <v>0</v>
       </c>
-      <c r="T69" s="2" t="n">
+      <c r="T69" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U69" t="n">
@@ -10753,7 +10497,7 @@
       <c r="S70" t="b">
         <v>0</v>
       </c>
-      <c r="T70" s="2" t="n">
+      <c r="T70" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U70" t="n">
@@ -10886,7 +10630,7 @@
       <c r="S71" t="b">
         <v>0</v>
       </c>
-      <c r="T71" s="2" t="n">
+      <c r="T71" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U71" t="n">
@@ -11019,7 +10763,7 @@
       <c r="S72" t="b">
         <v>0</v>
       </c>
-      <c r="T72" s="2" t="n">
+      <c r="T72" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U72" t="n">
@@ -11152,7 +10896,7 @@
       <c r="S73" t="b">
         <v>0</v>
       </c>
-      <c r="T73" s="2" t="n">
+      <c r="T73" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U73" t="n">
@@ -11285,7 +11029,7 @@
       <c r="S74" t="b">
         <v>0</v>
       </c>
-      <c r="T74" s="2" t="n">
+      <c r="T74" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U74" t="n">
@@ -11418,7 +11162,7 @@
       <c r="S75" t="b">
         <v>0</v>
       </c>
-      <c r="T75" s="2" t="n">
+      <c r="T75" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U75" t="n">
@@ -11551,7 +11295,7 @@
       <c r="S76" t="b">
         <v>0</v>
       </c>
-      <c r="T76" s="2" t="n">
+      <c r="T76" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U76" t="n">
@@ -11684,7 +11428,7 @@
       <c r="S77" t="b">
         <v>0</v>
       </c>
-      <c r="T77" s="2" t="n">
+      <c r="T77" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U77" t="n">
@@ -11817,7 +11561,7 @@
       <c r="S78" t="b">
         <v>0</v>
       </c>
-      <c r="T78" s="2" t="n">
+      <c r="T78" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U78" t="n">
@@ -11950,7 +11694,7 @@
       <c r="S79" t="b">
         <v>0</v>
       </c>
-      <c r="T79" s="2" t="n">
+      <c r="T79" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U79" t="n">
@@ -12083,7 +11827,7 @@
       <c r="S80" t="b">
         <v>0</v>
       </c>
-      <c r="T80" s="2" t="n">
+      <c r="T80" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U80" t="n">
@@ -12216,7 +11960,7 @@
       <c r="S81" t="b">
         <v>0</v>
       </c>
-      <c r="T81" s="2" t="n">
+      <c r="T81" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U81" t="n">
@@ -12349,7 +12093,7 @@
       <c r="S82" t="b">
         <v>0</v>
       </c>
-      <c r="T82" s="2" t="n">
+      <c r="T82" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U82" t="n">
@@ -12482,7 +12226,7 @@
       <c r="S83" t="b">
         <v>0</v>
       </c>
-      <c r="T83" s="2" t="n">
+      <c r="T83" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U83" t="n">
@@ -12615,7 +12359,7 @@
       <c r="S84" t="b">
         <v>0</v>
       </c>
-      <c r="T84" s="2" t="n">
+      <c r="T84" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U84" t="n">
@@ -12748,7 +12492,7 @@
       <c r="S85" t="b">
         <v>0</v>
       </c>
-      <c r="T85" s="2" t="n">
+      <c r="T85" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U85" t="n">
@@ -12881,7 +12625,7 @@
       <c r="S86" t="b">
         <v>0</v>
       </c>
-      <c r="T86" s="2" t="n">
+      <c r="T86" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U86" t="n">
@@ -13014,7 +12758,7 @@
       <c r="S87" t="b">
         <v>0</v>
       </c>
-      <c r="T87" s="2" t="n">
+      <c r="T87" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U87" t="n">
@@ -13147,7 +12891,7 @@
       <c r="S88" t="b">
         <v>0</v>
       </c>
-      <c r="T88" s="2" t="n">
+      <c r="T88" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U88" t="n">
@@ -13280,7 +13024,7 @@
       <c r="S89" t="b">
         <v>0</v>
       </c>
-      <c r="T89" s="2" t="n">
+      <c r="T89" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U89" t="n">
@@ -13413,7 +13157,7 @@
       <c r="S90" t="b">
         <v>0</v>
       </c>
-      <c r="T90" s="2" t="n">
+      <c r="T90" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U90" t="n">
@@ -13546,7 +13290,7 @@
       <c r="S91" t="b">
         <v>0</v>
       </c>
-      <c r="T91" s="2" t="n">
+      <c r="T91" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U91" t="n">
@@ -13679,7 +13423,7 @@
       <c r="S92" t="b">
         <v>0</v>
       </c>
-      <c r="T92" s="2" t="n">
+      <c r="T92" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U92" t="n">
@@ -13812,7 +13556,7 @@
       <c r="S93" t="b">
         <v>0</v>
       </c>
-      <c r="T93" s="2" t="n">
+      <c r="T93" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U93" t="n">
@@ -13945,7 +13689,7 @@
       <c r="S94" t="b">
         <v>0</v>
       </c>
-      <c r="T94" s="2" t="n">
+      <c r="T94" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U94" t="n">
@@ -14078,7 +13822,7 @@
       <c r="S95" t="b">
         <v>0</v>
       </c>
-      <c r="T95" s="2" t="n">
+      <c r="T95" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U95" t="n">
@@ -14211,7 +13955,7 @@
       <c r="S96" t="b">
         <v>0</v>
       </c>
-      <c r="T96" s="2" t="n">
+      <c r="T96" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U96" t="n">
@@ -14344,7 +14088,7 @@
       <c r="S97" t="b">
         <v>0</v>
       </c>
-      <c r="T97" s="2" t="n">
+      <c r="T97" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U97" t="n">
@@ -14477,7 +14221,7 @@
       <c r="S98" t="b">
         <v>0</v>
       </c>
-      <c r="T98" s="2" t="n">
+      <c r="T98" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U98" t="n">
@@ -14610,7 +14354,7 @@
       <c r="S99" t="b">
         <v>0</v>
       </c>
-      <c r="T99" s="2" t="n">
+      <c r="T99" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U99" t="n">
@@ -14743,7 +14487,7 @@
       <c r="S100" t="b">
         <v>0</v>
       </c>
-      <c r="T100" s="2" t="n">
+      <c r="T100" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U100" t="n">
@@ -14876,7 +14620,7 @@
       <c r="S101" t="b">
         <v>0</v>
       </c>
-      <c r="T101" s="2" t="n">
+      <c r="T101" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U101" t="n">
@@ -15009,7 +14753,7 @@
       <c r="S102" t="b">
         <v>0</v>
       </c>
-      <c r="T102" s="2" t="n">
+      <c r="T102" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U102" t="n">
@@ -15142,7 +14886,7 @@
       <c r="S103" t="b">
         <v>0</v>
       </c>
-      <c r="T103" s="2" t="n">
+      <c r="T103" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U103" t="n">
@@ -15275,7 +15019,7 @@
       <c r="S104" t="b">
         <v>0</v>
       </c>
-      <c r="T104" s="2" t="n">
+      <c r="T104" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U104" t="n">
@@ -15408,7 +15152,7 @@
       <c r="S105" t="b">
         <v>0</v>
       </c>
-      <c r="T105" s="2" t="n">
+      <c r="T105" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U105" t="n">
@@ -15541,7 +15285,7 @@
       <c r="S106" t="b">
         <v>0</v>
       </c>
-      <c r="T106" s="2" t="n">
+      <c r="T106" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U106" t="n">
@@ -15674,7 +15418,7 @@
       <c r="S107" t="b">
         <v>0</v>
       </c>
-      <c r="T107" s="2" t="n">
+      <c r="T107" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U107" t="n">
@@ -15807,7 +15551,7 @@
       <c r="S108" t="b">
         <v>0</v>
       </c>
-      <c r="T108" s="2" t="n">
+      <c r="T108" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U108" t="n">
@@ -15940,7 +15684,7 @@
       <c r="S109" t="b">
         <v>0</v>
       </c>
-      <c r="T109" s="2" t="n">
+      <c r="T109" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U109" t="n">
@@ -16073,7 +15817,7 @@
       <c r="S110" t="b">
         <v>0</v>
       </c>
-      <c r="T110" s="2" t="n">
+      <c r="T110" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U110" t="n">
@@ -16206,7 +15950,7 @@
       <c r="S111" t="b">
         <v>0</v>
       </c>
-      <c r="T111" s="2" t="n">
+      <c r="T111" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U111" t="n">
@@ -16339,7 +16083,7 @@
       <c r="S112" t="b">
         <v>0</v>
       </c>
-      <c r="T112" s="2" t="n">
+      <c r="T112" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U112" t="n">
@@ -16472,7 +16216,7 @@
       <c r="S113" t="b">
         <v>0</v>
       </c>
-      <c r="T113" s="2" t="n">
+      <c r="T113" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U113" t="n">
@@ -16605,7 +16349,7 @@
       <c r="S114" t="b">
         <v>0</v>
       </c>
-      <c r="T114" s="2" t="n">
+      <c r="T114" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U114" t="n">
@@ -16738,7 +16482,7 @@
       <c r="S115" t="b">
         <v>0</v>
       </c>
-      <c r="T115" s="2" t="n">
+      <c r="T115" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U115" t="n">
@@ -16871,7 +16615,7 @@
       <c r="S116" t="b">
         <v>0</v>
       </c>
-      <c r="T116" s="2" t="n">
+      <c r="T116" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U116" t="n">
@@ -17004,7 +16748,7 @@
       <c r="S117" t="b">
         <v>0</v>
       </c>
-      <c r="T117" s="2" t="n">
+      <c r="T117" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U117" t="n">
@@ -17137,7 +16881,7 @@
       <c r="S118" t="b">
         <v>0</v>
       </c>
-      <c r="T118" s="2" t="n">
+      <c r="T118" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U118" t="n">
@@ -17270,7 +17014,7 @@
       <c r="S119" t="b">
         <v>0</v>
       </c>
-      <c r="T119" s="2" t="n">
+      <c r="T119" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U119" t="n">
@@ -17403,7 +17147,7 @@
       <c r="S120" t="b">
         <v>0</v>
       </c>
-      <c r="T120" s="2" t="n">
+      <c r="T120" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U120" t="n">
@@ -17536,7 +17280,7 @@
       <c r="S121" t="b">
         <v>0</v>
       </c>
-      <c r="T121" s="2" t="n">
+      <c r="T121" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U121" t="n">
@@ -17669,7 +17413,7 @@
       <c r="S122" t="b">
         <v>0</v>
       </c>
-      <c r="T122" s="2" t="n">
+      <c r="T122" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U122" t="n">
@@ -17802,7 +17546,7 @@
       <c r="S123" t="b">
         <v>0</v>
       </c>
-      <c r="T123" s="2" t="n">
+      <c r="T123" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U123" t="n">
@@ -17935,7 +17679,7 @@
       <c r="S124" t="b">
         <v>0</v>
       </c>
-      <c r="T124" s="2" t="n">
+      <c r="T124" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U124" t="n">
@@ -18068,7 +17812,7 @@
       <c r="S125" t="b">
         <v>0</v>
       </c>
-      <c r="T125" s="2" t="n">
+      <c r="T125" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U125" t="n">
@@ -18201,7 +17945,7 @@
       <c r="S126" t="b">
         <v>0</v>
       </c>
-      <c r="T126" s="2" t="n">
+      <c r="T126" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U126" t="n">
@@ -18334,7 +18078,7 @@
       <c r="S127" t="b">
         <v>0</v>
       </c>
-      <c r="T127" s="2" t="n">
+      <c r="T127" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U127" t="n">
@@ -18467,7 +18211,7 @@
       <c r="S128" t="b">
         <v>0</v>
       </c>
-      <c r="T128" s="2" t="n">
+      <c r="T128" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U128" t="n">
@@ -18600,7 +18344,7 @@
       <c r="S129" t="b">
         <v>0</v>
       </c>
-      <c r="T129" s="2" t="n">
+      <c r="T129" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U129" t="n">
@@ -18733,7 +18477,7 @@
       <c r="S130" t="b">
         <v>0</v>
       </c>
-      <c r="T130" s="2" t="n">
+      <c r="T130" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U130" t="n">
@@ -18866,7 +18610,7 @@
       <c r="S131" t="b">
         <v>0</v>
       </c>
-      <c r="T131" s="2" t="n">
+      <c r="T131" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U131" t="n">
@@ -18999,7 +18743,7 @@
       <c r="S132" t="b">
         <v>0</v>
       </c>
-      <c r="T132" s="2" t="n">
+      <c r="T132" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U132" t="n">
@@ -19132,7 +18876,7 @@
       <c r="S133" t="b">
         <v>0</v>
       </c>
-      <c r="T133" s="2" t="n">
+      <c r="T133" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U133" t="n">
@@ -19265,7 +19009,7 @@
       <c r="S134" t="b">
         <v>0</v>
       </c>
-      <c r="T134" s="2" t="n">
+      <c r="T134" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U134" t="n">
@@ -19398,7 +19142,7 @@
       <c r="S135" t="b">
         <v>0</v>
       </c>
-      <c r="T135" s="2" t="n">
+      <c r="T135" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U135" t="n">
@@ -19531,7 +19275,7 @@
       <c r="S136" t="b">
         <v>0</v>
       </c>
-      <c r="T136" s="2" t="n">
+      <c r="T136" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U136" t="n">
@@ -19664,7 +19408,7 @@
       <c r="S137" t="b">
         <v>0</v>
       </c>
-      <c r="T137" s="2" t="n">
+      <c r="T137" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U137" t="n">
@@ -19797,7 +19541,7 @@
       <c r="S138" t="b">
         <v>0</v>
       </c>
-      <c r="T138" s="2" t="n">
+      <c r="T138" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U138" t="n">
@@ -19930,7 +19674,7 @@
       <c r="S139" t="b">
         <v>0</v>
       </c>
-      <c r="T139" s="2" t="n">
+      <c r="T139" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U139" t="n">
@@ -20063,7 +19807,7 @@
       <c r="S140" t="b">
         <v>0</v>
       </c>
-      <c r="T140" s="2" t="n">
+      <c r="T140" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U140" t="n">
@@ -20196,7 +19940,7 @@
       <c r="S141" t="b">
         <v>0</v>
       </c>
-      <c r="T141" s="2" t="n">
+      <c r="T141" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U141" t="n">
@@ -20329,7 +20073,7 @@
       <c r="S142" t="b">
         <v>0</v>
       </c>
-      <c r="T142" s="2" t="n">
+      <c r="T142" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U142" t="n">
@@ -20462,7 +20206,7 @@
       <c r="S143" t="b">
         <v>0</v>
       </c>
-      <c r="T143" s="2" t="n">
+      <c r="T143" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U143" t="n">
@@ -20595,7 +20339,7 @@
       <c r="S144" t="b">
         <v>0</v>
       </c>
-      <c r="T144" s="2" t="n">
+      <c r="T144" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U144" t="n">
@@ -20728,7 +20472,7 @@
       <c r="S145" t="b">
         <v>0</v>
       </c>
-      <c r="T145" s="2" t="n">
+      <c r="T145" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U145" t="n">
@@ -20861,7 +20605,7 @@
       <c r="S146" t="b">
         <v>0</v>
       </c>
-      <c r="T146" s="2" t="n">
+      <c r="T146" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U146" t="n">
@@ -20994,7 +20738,7 @@
       <c r="S147" t="b">
         <v>0</v>
       </c>
-      <c r="T147" s="2" t="n">
+      <c r="T147" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U147" t="n">
@@ -21127,7 +20871,7 @@
       <c r="S148" t="b">
         <v>0</v>
       </c>
-      <c r="T148" s="2" t="n">
+      <c r="T148" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U148" t="n">
@@ -21260,7 +21004,7 @@
       <c r="S149" t="b">
         <v>0</v>
       </c>
-      <c r="T149" s="2" t="n">
+      <c r="T149" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U149" t="n">
@@ -21393,7 +21137,7 @@
       <c r="S150" t="b">
         <v>0</v>
       </c>
-      <c r="T150" s="2" t="n">
+      <c r="T150" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U150" t="n">
@@ -21526,7 +21270,7 @@
       <c r="S151" t="b">
         <v>0</v>
       </c>
-      <c r="T151" s="2" t="n">
+      <c r="T151" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U151" t="n">
@@ -21659,7 +21403,7 @@
       <c r="S152" t="b">
         <v>0</v>
       </c>
-      <c r="T152" s="2" t="n">
+      <c r="T152" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U152" t="n">
@@ -21792,7 +21536,7 @@
       <c r="S153" t="b">
         <v>0</v>
       </c>
-      <c r="T153" s="2" t="n">
+      <c r="T153" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U153" t="n">
@@ -21925,7 +21669,7 @@
       <c r="S154" t="b">
         <v>0</v>
       </c>
-      <c r="T154" s="2" t="n">
+      <c r="T154" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U154" t="n">
@@ -22058,7 +21802,7 @@
       <c r="S155" t="b">
         <v>0</v>
       </c>
-      <c r="T155" s="2" t="n">
+      <c r="T155" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U155" t="n">
@@ -22191,7 +21935,7 @@
       <c r="S156" t="b">
         <v>0</v>
       </c>
-      <c r="T156" s="2" t="n">
+      <c r="T156" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U156" t="n">
@@ -22324,7 +22068,7 @@
       <c r="S157" t="b">
         <v>0</v>
       </c>
-      <c r="T157" s="2" t="n">
+      <c r="T157" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U157" t="n">
@@ -22457,7 +22201,7 @@
       <c r="S158" t="b">
         <v>0</v>
       </c>
-      <c r="T158" s="2" t="n">
+      <c r="T158" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U158" t="n">
@@ -22590,7 +22334,7 @@
       <c r="S159" t="b">
         <v>0</v>
       </c>
-      <c r="T159" s="2" t="n">
+      <c r="T159" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U159" t="n">
@@ -22723,7 +22467,7 @@
       <c r="S160" t="b">
         <v>0</v>
       </c>
-      <c r="T160" s="2" t="n">
+      <c r="T160" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U160" t="n">
@@ -22856,7 +22600,7 @@
       <c r="S161" t="b">
         <v>0</v>
       </c>
-      <c r="T161" s="2" t="n">
+      <c r="T161" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U161" t="n">
@@ -22989,7 +22733,7 @@
       <c r="S162" t="b">
         <v>0</v>
       </c>
-      <c r="T162" s="2" t="n">
+      <c r="T162" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U162" t="n">
@@ -23122,7 +22866,7 @@
       <c r="S163" t="b">
         <v>0</v>
       </c>
-      <c r="T163" s="2" t="n">
+      <c r="T163" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U163" t="n">
@@ -23255,7 +22999,7 @@
       <c r="S164" t="b">
         <v>0</v>
       </c>
-      <c r="T164" s="2" t="n">
+      <c r="T164" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U164" t="n">
@@ -23388,7 +23132,7 @@
       <c r="S165" t="b">
         <v>0</v>
       </c>
-      <c r="T165" s="2" t="n">
+      <c r="T165" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U165" t="n">
@@ -23521,7 +23265,7 @@
       <c r="S166" t="b">
         <v>0</v>
       </c>
-      <c r="T166" s="2" t="n">
+      <c r="T166" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U166" t="n">
@@ -23654,7 +23398,7 @@
       <c r="S167" t="b">
         <v>0</v>
       </c>
-      <c r="T167" s="2" t="n">
+      <c r="T167" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U167" t="n">
@@ -23787,7 +23531,7 @@
       <c r="S168" t="b">
         <v>0</v>
       </c>
-      <c r="T168" s="2" t="n">
+      <c r="T168" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U168" t="n">
@@ -23920,7 +23664,7 @@
       <c r="S169" t="b">
         <v>0</v>
       </c>
-      <c r="T169" s="2" t="n">
+      <c r="T169" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U169" t="n">
@@ -24053,7 +23797,7 @@
       <c r="S170" t="b">
         <v>0</v>
       </c>
-      <c r="T170" s="2" t="n">
+      <c r="T170" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U170" t="n">
@@ -24186,7 +23930,7 @@
       <c r="S171" t="b">
         <v>0</v>
       </c>
-      <c r="T171" s="2" t="n">
+      <c r="T171" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U171" t="n">
@@ -24319,7 +24063,7 @@
       <c r="S172" t="b">
         <v>0</v>
       </c>
-      <c r="T172" s="2" t="n">
+      <c r="T172" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U172" t="n">
@@ -24452,7 +24196,7 @@
       <c r="S173" t="b">
         <v>0</v>
       </c>
-      <c r="T173" s="2" t="n">
+      <c r="T173" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U173" t="n">
@@ -24585,7 +24329,7 @@
       <c r="S174" t="b">
         <v>0</v>
       </c>
-      <c r="T174" s="2" t="n">
+      <c r="T174" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U174" t="n">
@@ -24718,7 +24462,7 @@
       <c r="S175" t="b">
         <v>0</v>
       </c>
-      <c r="T175" s="2" t="n">
+      <c r="T175" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U175" t="n">
@@ -24851,7 +24595,7 @@
       <c r="S176" t="b">
         <v>0</v>
       </c>
-      <c r="T176" s="2" t="n">
+      <c r="T176" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U176" t="n">
@@ -24984,7 +24728,7 @@
       <c r="S177" t="b">
         <v>0</v>
       </c>
-      <c r="T177" s="2" t="n">
+      <c r="T177" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U177" t="n">
@@ -25117,7 +24861,7 @@
       <c r="S178" t="b">
         <v>0</v>
       </c>
-      <c r="T178" s="2" t="n">
+      <c r="T178" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U178" t="n">
@@ -25250,7 +24994,7 @@
       <c r="S179" t="b">
         <v>0</v>
       </c>
-      <c r="T179" s="2" t="n">
+      <c r="T179" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U179" t="n">
@@ -25383,7 +25127,7 @@
       <c r="S180" t="b">
         <v>0</v>
       </c>
-      <c r="T180" s="2" t="n">
+      <c r="T180" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U180" t="n">
@@ -25516,7 +25260,7 @@
       <c r="S181" t="b">
         <v>0</v>
       </c>
-      <c r="T181" s="2" t="n">
+      <c r="T181" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U181" t="n">
@@ -25649,7 +25393,7 @@
       <c r="S182" t="b">
         <v>0</v>
       </c>
-      <c r="T182" s="2" t="n">
+      <c r="T182" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U182" t="n">
@@ -25782,7 +25526,7 @@
       <c r="S183" t="b">
         <v>0</v>
       </c>
-      <c r="T183" s="2" t="n">
+      <c r="T183" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U183" t="n">
@@ -25915,7 +25659,7 @@
       <c r="S184" t="b">
         <v>0</v>
       </c>
-      <c r="T184" s="2" t="n">
+      <c r="T184" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U184" t="n">
@@ -26048,7 +25792,7 @@
       <c r="S185" t="b">
         <v>0</v>
       </c>
-      <c r="T185" s="2" t="n">
+      <c r="T185" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U185" t="n">
@@ -26181,7 +25925,7 @@
       <c r="S186" t="b">
         <v>0</v>
       </c>
-      <c r="T186" s="2" t="n">
+      <c r="T186" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U186" t="n">
@@ -26314,7 +26058,7 @@
       <c r="S187" t="b">
         <v>0</v>
       </c>
-      <c r="T187" s="2" t="n">
+      <c r="T187" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U187" t="n">
@@ -26447,7 +26191,7 @@
       <c r="S188" t="b">
         <v>0</v>
       </c>
-      <c r="T188" s="2" t="n">
+      <c r="T188" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U188" t="n">
@@ -26580,7 +26324,7 @@
       <c r="S189" t="b">
         <v>0</v>
       </c>
-      <c r="T189" s="2" t="n">
+      <c r="T189" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U189" t="n">
@@ -26713,7 +26457,7 @@
       <c r="S190" t="b">
         <v>0</v>
       </c>
-      <c r="T190" s="2" t="n">
+      <c r="T190" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U190" t="n">
@@ -26846,7 +26590,7 @@
       <c r="S191" t="b">
         <v>0</v>
       </c>
-      <c r="T191" s="2" t="n">
+      <c r="T191" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U191" t="n">
@@ -26893,6 +26637,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Customer" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aging" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Trend" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="By Customer" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aging" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily Trend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,16 +24,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -142,246 +130,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>Generated by TRAE AI</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -668,7 +416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -677,12 +425,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -725,17 +473,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -744,27 +491,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>open_shipments</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>total_outstanding</t>
         </is>
@@ -1117,12 +864,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1131,12 +877,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>aging_bucket</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
@@ -1149,7 +895,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>534506200.98</v>
+        <v>533200026.29</v>
       </c>
     </row>
     <row r="3">
@@ -1159,7 +905,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52269015.54</v>
+        <v>53575190.23</v>
       </c>
     </row>
     <row r="4">
@@ -1184,12 +930,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1198,252 +943,252 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>collected</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46134</v>
+      <c r="A2" s="1" t="n">
+        <v>46135</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>10281291.96</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46135</v>
+      <c r="A3" s="1" t="n">
+        <v>46136</v>
       </c>
       <c r="B3" t="n">
-        <v>10281291.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46136</v>
+      <c r="A4" s="1" t="n">
+        <v>46137</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>11750336.82</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46137</v>
+      <c r="A5" s="1" t="n">
+        <v>46138</v>
       </c>
       <c r="B5" t="n">
-        <v>11750336.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46138</v>
+      <c r="A6" s="1" t="n">
+        <v>46139</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>18312295.73</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>46139</v>
+      <c r="A7" s="1" t="n">
+        <v>46140</v>
       </c>
       <c r="B7" t="n">
-        <v>18312295.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>46140</v>
+      <c r="A8" s="1" t="n">
+        <v>46141</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>4194477.04</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>46141</v>
+      <c r="A9" s="1" t="n">
+        <v>46142</v>
       </c>
       <c r="B9" t="n">
-        <v>4194477.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>46142</v>
+      <c r="A10" s="1" t="n">
+        <v>46143</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>46143</v>
+      <c r="A11" s="1" t="n">
+        <v>46144</v>
       </c>
       <c r="B11" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46144</v>
+      <c r="A12" s="1" t="n">
+        <v>46145</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>46145</v>
+      <c r="A13" s="1" t="n">
+        <v>46146</v>
       </c>
       <c r="B13" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>46146</v>
+      <c r="A14" s="1" t="n">
+        <v>46147</v>
       </c>
       <c r="B14" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46147</v>
+      <c r="A15" s="1" t="n">
+        <v>46148</v>
       </c>
       <c r="B15" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46148</v>
+      <c r="A16" s="1" t="n">
+        <v>46149</v>
       </c>
       <c r="B16" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46149</v>
+      <c r="A17" s="1" t="n">
+        <v>46150</v>
       </c>
       <c r="B17" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46150</v>
+      <c r="A18" s="1" t="n">
+        <v>46151</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46151</v>
+      <c r="A19" s="1" t="n">
+        <v>46152</v>
       </c>
       <c r="B19" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46152</v>
+      <c r="A20" s="1" t="n">
+        <v>46153</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46153</v>
+      <c r="A21" s="1" t="n">
+        <v>46154</v>
       </c>
       <c r="B21" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46154</v>
+      <c r="A22" s="1" t="n">
+        <v>46155</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46155</v>
+      <c r="A23" s="1" t="n">
+        <v>46156</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46156</v>
+      <c r="A24" s="1" t="n">
+        <v>46157</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46157</v>
+      <c r="A25" s="1" t="n">
+        <v>46158</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46158</v>
+      <c r="A26" s="1" t="n">
+        <v>46159</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46159</v>
+      <c r="A27" s="1" t="n">
+        <v>46160</v>
       </c>
       <c r="B27" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46160</v>
+      <c r="A28" s="1" t="n">
+        <v>46161</v>
       </c>
       <c r="B28" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46161</v>
+      <c r="A29" s="1" t="n">
+        <v>46162</v>
       </c>
       <c r="B29" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46162</v>
+      <c r="A30" s="1" t="n">
+        <v>46163</v>
       </c>
       <c r="B30" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46163</v>
+      <c r="A31" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1451,12 +1196,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1465,157 +1209,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>shipment_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>material_category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>material_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>quantity_mt</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>rate_per_mt</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sale_value_without_gst</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gst_rate_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gst_amount</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>invoice_amount</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>shipment_date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>delivered_date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>invoice_date</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>vehicle_number</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>sales_order_id</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>amount_paid_total</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>outstanding</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>is_settled</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>due_date_parsed</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>days_to_due</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>days_overdue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>eligible_for_reminder</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>eligible_for_overdue</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>in_7d_window</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>in_3d_window</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>in_1d_window</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>aging_bucket</t>
         </is>
@@ -1709,14 +1453,14 @@
       <c r="S2" t="b">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="V2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1842,14 +1586,14 @@
       <c r="S3" t="b">
         <v>0</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="T3" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-65</v>
+        <v>-66</v>
       </c>
       <c r="V3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1975,14 +1719,14 @@
       <c r="S4" t="b">
         <v>0</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="V4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -2108,14 +1852,14 @@
       <c r="S5" t="b">
         <v>0</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="V5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -2241,14 +1985,14 @@
       <c r="S6" t="b">
         <v>0</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="V6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2374,14 +2118,14 @@
       <c r="S7" t="b">
         <v>0</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" s="1" t="n">
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="V7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2507,14 +2251,14 @@
       <c r="S8" t="b">
         <v>0</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2640,11 +2384,11 @@
       <c r="S9" t="b">
         <v>0</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="T9" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2773,11 +2517,11 @@
       <c r="S10" t="b">
         <v>0</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="T10" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2906,11 +2650,11 @@
       <c r="S11" t="b">
         <v>0</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="T11" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -3039,14 +2783,14 @@
       <c r="S12" t="b">
         <v>0</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="T12" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -3172,14 +2916,14 @@
       <c r="S13" t="b">
         <v>0</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="T13" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3200,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="b">
         <v>0</v>
@@ -3213,7 +2957,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Not Yet Due</t>
+          <t>1-30 Days Overdue</t>
         </is>
       </c>
     </row>
@@ -3305,11 +3049,11 @@
       <c r="S14" t="b">
         <v>0</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="T14" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3438,11 +3182,11 @@
       <c r="S15" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="T15" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3571,11 +3315,11 @@
       <c r="S16" t="b">
         <v>0</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="T16" s="1" t="n">
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3704,11 +3448,11 @@
       <c r="S17" t="b">
         <v>0</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="T17" s="1" t="n">
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3837,11 +3581,11 @@
       <c r="S18" t="b">
         <v>0</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="T18" s="1" t="n">
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3970,11 +3714,11 @@
       <c r="S19" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="T19" s="1" t="n">
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4103,11 +3847,11 @@
       <c r="S20" t="b">
         <v>0</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="T20" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4236,11 +3980,11 @@
       <c r="S21" t="b">
         <v>0</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="T21" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4369,11 +4113,11 @@
       <c r="S22" t="b">
         <v>0</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="T22" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4502,11 +4246,11 @@
       <c r="S23" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="T23" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4635,11 +4379,11 @@
       <c r="S24" t="b">
         <v>0</v>
       </c>
-      <c r="T24" s="2" t="n">
+      <c r="T24" s="1" t="n">
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4768,11 +4512,11 @@
       <c r="S25" t="b">
         <v>0</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="T25" s="1" t="n">
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4901,11 +4645,11 @@
       <c r="S26" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="2" t="n">
+      <c r="T26" s="1" t="n">
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5034,11 +4778,11 @@
       <c r="S27" t="b">
         <v>0</v>
       </c>
-      <c r="T27" s="2" t="n">
+      <c r="T27" s="1" t="n">
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5167,11 +4911,11 @@
       <c r="S28" t="b">
         <v>0</v>
       </c>
-      <c r="T28" s="2" t="n">
+      <c r="T28" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5300,11 +5044,11 @@
       <c r="S29" t="b">
         <v>0</v>
       </c>
-      <c r="T29" s="2" t="n">
+      <c r="T29" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5433,11 +5177,11 @@
       <c r="S30" t="b">
         <v>0</v>
       </c>
-      <c r="T30" s="2" t="n">
+      <c r="T30" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5566,11 +5310,11 @@
       <c r="S31" t="b">
         <v>0</v>
       </c>
-      <c r="T31" s="2" t="n">
+      <c r="T31" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5699,11 +5443,11 @@
       <c r="S32" t="b">
         <v>0</v>
       </c>
-      <c r="T32" s="2" t="n">
+      <c r="T32" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5832,11 +5576,11 @@
       <c r="S33" t="b">
         <v>0</v>
       </c>
-      <c r="T33" s="2" t="n">
+      <c r="T33" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5965,11 +5709,11 @@
       <c r="S34" t="b">
         <v>0</v>
       </c>
-      <c r="T34" s="2" t="n">
+      <c r="T34" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -6098,11 +5842,11 @@
       <c r="S35" t="b">
         <v>0</v>
       </c>
-      <c r="T35" s="2" t="n">
+      <c r="T35" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -6231,11 +5975,11 @@
       <c r="S36" t="b">
         <v>0</v>
       </c>
-      <c r="T36" s="2" t="n">
+      <c r="T36" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6364,11 +6108,11 @@
       <c r="S37" t="b">
         <v>0</v>
       </c>
-      <c r="T37" s="2" t="n">
+      <c r="T37" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6497,11 +6241,11 @@
       <c r="S38" t="b">
         <v>0</v>
       </c>
-      <c r="T38" s="2" t="n">
+      <c r="T38" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6630,11 +6374,11 @@
       <c r="S39" t="b">
         <v>0</v>
       </c>
-      <c r="T39" s="2" t="n">
+      <c r="T39" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6763,11 +6507,11 @@
       <c r="S40" t="b">
         <v>0</v>
       </c>
-      <c r="T40" s="2" t="n">
+      <c r="T40" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6896,11 +6640,11 @@
       <c r="S41" t="b">
         <v>0</v>
       </c>
-      <c r="T41" s="2" t="n">
+      <c r="T41" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7029,11 +6773,11 @@
       <c r="S42" t="b">
         <v>0</v>
       </c>
-      <c r="T42" s="2" t="n">
+      <c r="T42" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -7162,11 +6906,11 @@
       <c r="S43" t="b">
         <v>0</v>
       </c>
-      <c r="T43" s="2" t="n">
+      <c r="T43" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7295,11 +7039,11 @@
       <c r="S44" t="b">
         <v>0</v>
       </c>
-      <c r="T44" s="2" t="n">
+      <c r="T44" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7428,11 +7172,11 @@
       <c r="S45" t="b">
         <v>0</v>
       </c>
-      <c r="T45" s="2" t="n">
+      <c r="T45" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7561,11 +7305,11 @@
       <c r="S46" t="b">
         <v>0</v>
       </c>
-      <c r="T46" s="2" t="n">
+      <c r="T46" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7694,11 +7438,11 @@
       <c r="S47" t="b">
         <v>0</v>
       </c>
-      <c r="T47" s="2" t="n">
+      <c r="T47" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7827,11 +7571,11 @@
       <c r="S48" t="b">
         <v>0</v>
       </c>
-      <c r="T48" s="2" t="n">
+      <c r="T48" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7960,11 +7704,11 @@
       <c r="S49" t="b">
         <v>0</v>
       </c>
-      <c r="T49" s="2" t="n">
+      <c r="T49" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -8093,11 +7837,11 @@
       <c r="S50" t="b">
         <v>0</v>
       </c>
-      <c r="T50" s="2" t="n">
+      <c r="T50" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -8226,11 +7970,11 @@
       <c r="S51" t="b">
         <v>0</v>
       </c>
-      <c r="T51" s="2" t="n">
+      <c r="T51" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8359,11 +8103,11 @@
       <c r="S52" t="b">
         <v>0</v>
       </c>
-      <c r="T52" s="2" t="n">
+      <c r="T52" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8492,11 +8236,11 @@
       <c r="S53" t="b">
         <v>0</v>
       </c>
-      <c r="T53" s="2" t="n">
+      <c r="T53" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8625,11 +8369,11 @@
       <c r="S54" t="b">
         <v>0</v>
       </c>
-      <c r="T54" s="2" t="n">
+      <c r="T54" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8758,11 +8502,11 @@
       <c r="S55" t="b">
         <v>0</v>
       </c>
-      <c r="T55" s="2" t="n">
+      <c r="T55" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8891,11 +8635,11 @@
       <c r="S56" t="b">
         <v>0</v>
       </c>
-      <c r="T56" s="2" t="n">
+      <c r="T56" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -9024,11 +8768,11 @@
       <c r="S57" t="b">
         <v>0</v>
       </c>
-      <c r="T57" s="2" t="n">
+      <c r="T57" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -9157,11 +8901,11 @@
       <c r="S58" t="b">
         <v>0</v>
       </c>
-      <c r="T58" s="2" t="n">
+      <c r="T58" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9290,11 +9034,11 @@
       <c r="S59" t="b">
         <v>0</v>
       </c>
-      <c r="T59" s="2" t="n">
+      <c r="T59" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9423,11 +9167,11 @@
       <c r="S60" t="b">
         <v>0</v>
       </c>
-      <c r="T60" s="2" t="n">
+      <c r="T60" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9556,11 +9300,11 @@
       <c r="S61" t="b">
         <v>0</v>
       </c>
-      <c r="T61" s="2" t="n">
+      <c r="T61" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9689,11 +9433,11 @@
       <c r="S62" t="b">
         <v>0</v>
       </c>
-      <c r="T62" s="2" t="n">
+      <c r="T62" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9822,11 +9566,11 @@
       <c r="S63" t="b">
         <v>0</v>
       </c>
-      <c r="T63" s="2" t="n">
+      <c r="T63" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9955,11 +9699,11 @@
       <c r="S64" t="b">
         <v>0</v>
       </c>
-      <c r="T64" s="2" t="n">
+      <c r="T64" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -10088,11 +9832,11 @@
       <c r="S65" t="b">
         <v>0</v>
       </c>
-      <c r="T65" s="2" t="n">
+      <c r="T65" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -10221,11 +9965,11 @@
       <c r="S66" t="b">
         <v>0</v>
       </c>
-      <c r="T66" s="2" t="n">
+      <c r="T66" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10354,11 +10098,11 @@
       <c r="S67" t="b">
         <v>0</v>
       </c>
-      <c r="T67" s="2" t="n">
+      <c r="T67" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10487,11 +10231,11 @@
       <c r="S68" t="b">
         <v>0</v>
       </c>
-      <c r="T68" s="2" t="n">
+      <c r="T68" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10620,11 +10364,11 @@
       <c r="S69" t="b">
         <v>0</v>
       </c>
-      <c r="T69" s="2" t="n">
+      <c r="T69" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10753,11 +10497,11 @@
       <c r="S70" t="b">
         <v>0</v>
       </c>
-      <c r="T70" s="2" t="n">
+      <c r="T70" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10886,11 +10630,11 @@
       <c r="S71" t="b">
         <v>0</v>
       </c>
-      <c r="T71" s="2" t="n">
+      <c r="T71" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -11019,11 +10763,11 @@
       <c r="S72" t="b">
         <v>0</v>
       </c>
-      <c r="T72" s="2" t="n">
+      <c r="T72" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -11152,11 +10896,11 @@
       <c r="S73" t="b">
         <v>0</v>
       </c>
-      <c r="T73" s="2" t="n">
+      <c r="T73" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11285,11 +11029,11 @@
       <c r="S74" t="b">
         <v>0</v>
       </c>
-      <c r="T74" s="2" t="n">
+      <c r="T74" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11418,11 +11162,11 @@
       <c r="S75" t="b">
         <v>0</v>
       </c>
-      <c r="T75" s="2" t="n">
+      <c r="T75" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11551,11 +11295,11 @@
       <c r="S76" t="b">
         <v>0</v>
       </c>
-      <c r="T76" s="2" t="n">
+      <c r="T76" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11684,11 +11428,11 @@
       <c r="S77" t="b">
         <v>0</v>
       </c>
-      <c r="T77" s="2" t="n">
+      <c r="T77" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11817,11 +11561,11 @@
       <c r="S78" t="b">
         <v>0</v>
       </c>
-      <c r="T78" s="2" t="n">
+      <c r="T78" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11950,11 +11694,11 @@
       <c r="S79" t="b">
         <v>0</v>
       </c>
-      <c r="T79" s="2" t="n">
+      <c r="T79" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -12083,11 +11827,11 @@
       <c r="S80" t="b">
         <v>0</v>
       </c>
-      <c r="T80" s="2" t="n">
+      <c r="T80" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -12216,11 +11960,11 @@
       <c r="S81" t="b">
         <v>0</v>
       </c>
-      <c r="T81" s="2" t="n">
+      <c r="T81" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12349,11 +12093,11 @@
       <c r="S82" t="b">
         <v>0</v>
       </c>
-      <c r="T82" s="2" t="n">
+      <c r="T82" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12482,11 +12226,11 @@
       <c r="S83" t="b">
         <v>0</v>
       </c>
-      <c r="T83" s="2" t="n">
+      <c r="T83" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12615,11 +12359,11 @@
       <c r="S84" t="b">
         <v>0</v>
       </c>
-      <c r="T84" s="2" t="n">
+      <c r="T84" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12748,11 +12492,11 @@
       <c r="S85" t="b">
         <v>0</v>
       </c>
-      <c r="T85" s="2" t="n">
+      <c r="T85" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12881,11 +12625,11 @@
       <c r="S86" t="b">
         <v>0</v>
       </c>
-      <c r="T86" s="2" t="n">
+      <c r="T86" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -13014,11 +12758,11 @@
       <c r="S87" t="b">
         <v>0</v>
       </c>
-      <c r="T87" s="2" t="n">
+      <c r="T87" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -13147,11 +12891,11 @@
       <c r="S88" t="b">
         <v>0</v>
       </c>
-      <c r="T88" s="2" t="n">
+      <c r="T88" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13280,11 +13024,11 @@
       <c r="S89" t="b">
         <v>0</v>
       </c>
-      <c r="T89" s="2" t="n">
+      <c r="T89" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13413,11 +13157,11 @@
       <c r="S90" t="b">
         <v>0</v>
       </c>
-      <c r="T90" s="2" t="n">
+      <c r="T90" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13546,11 +13290,11 @@
       <c r="S91" t="b">
         <v>0</v>
       </c>
-      <c r="T91" s="2" t="n">
+      <c r="T91" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13679,11 +13423,11 @@
       <c r="S92" t="b">
         <v>0</v>
       </c>
-      <c r="T92" s="2" t="n">
+      <c r="T92" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13812,11 +13556,11 @@
       <c r="S93" t="b">
         <v>0</v>
       </c>
-      <c r="T93" s="2" t="n">
+      <c r="T93" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13945,11 +13689,11 @@
       <c r="S94" t="b">
         <v>0</v>
       </c>
-      <c r="T94" s="2" t="n">
+      <c r="T94" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -14078,11 +13822,11 @@
       <c r="S95" t="b">
         <v>0</v>
       </c>
-      <c r="T95" s="2" t="n">
+      <c r="T95" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -14211,11 +13955,11 @@
       <c r="S96" t="b">
         <v>0</v>
       </c>
-      <c r="T96" s="2" t="n">
+      <c r="T96" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14344,11 +14088,11 @@
       <c r="S97" t="b">
         <v>0</v>
       </c>
-      <c r="T97" s="2" t="n">
+      <c r="T97" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14477,11 +14221,11 @@
       <c r="S98" t="b">
         <v>0</v>
       </c>
-      <c r="T98" s="2" t="n">
+      <c r="T98" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14610,11 +14354,11 @@
       <c r="S99" t="b">
         <v>0</v>
       </c>
-      <c r="T99" s="2" t="n">
+      <c r="T99" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14743,11 +14487,11 @@
       <c r="S100" t="b">
         <v>0</v>
       </c>
-      <c r="T100" s="2" t="n">
+      <c r="T100" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14876,11 +14620,11 @@
       <c r="S101" t="b">
         <v>0</v>
       </c>
-      <c r="T101" s="2" t="n">
+      <c r="T101" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -15009,11 +14753,11 @@
       <c r="S102" t="b">
         <v>0</v>
       </c>
-      <c r="T102" s="2" t="n">
+      <c r="T102" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -15142,11 +14886,11 @@
       <c r="S103" t="b">
         <v>0</v>
       </c>
-      <c r="T103" s="2" t="n">
+      <c r="T103" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15275,11 +15019,11 @@
       <c r="S104" t="b">
         <v>0</v>
       </c>
-      <c r="T104" s="2" t="n">
+      <c r="T104" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15408,11 +15152,11 @@
       <c r="S105" t="b">
         <v>0</v>
       </c>
-      <c r="T105" s="2" t="n">
+      <c r="T105" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15541,11 +15285,11 @@
       <c r="S106" t="b">
         <v>0</v>
       </c>
-      <c r="T106" s="2" t="n">
+      <c r="T106" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15674,11 +15418,11 @@
       <c r="S107" t="b">
         <v>0</v>
       </c>
-      <c r="T107" s="2" t="n">
+      <c r="T107" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15807,11 +15551,11 @@
       <c r="S108" t="b">
         <v>0</v>
       </c>
-      <c r="T108" s="2" t="n">
+      <c r="T108" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15940,11 +15684,11 @@
       <c r="S109" t="b">
         <v>0</v>
       </c>
-      <c r="T109" s="2" t="n">
+      <c r="T109" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -16073,11 +15817,11 @@
       <c r="S110" t="b">
         <v>0</v>
       </c>
-      <c r="T110" s="2" t="n">
+      <c r="T110" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -16206,11 +15950,11 @@
       <c r="S111" t="b">
         <v>0</v>
       </c>
-      <c r="T111" s="2" t="n">
+      <c r="T111" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16339,11 +16083,11 @@
       <c r="S112" t="b">
         <v>0</v>
       </c>
-      <c r="T112" s="2" t="n">
+      <c r="T112" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16472,11 +16216,11 @@
       <c r="S113" t="b">
         <v>0</v>
       </c>
-      <c r="T113" s="2" t="n">
+      <c r="T113" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16605,11 +16349,11 @@
       <c r="S114" t="b">
         <v>0</v>
       </c>
-      <c r="T114" s="2" t="n">
+      <c r="T114" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16738,11 +16482,11 @@
       <c r="S115" t="b">
         <v>0</v>
       </c>
-      <c r="T115" s="2" t="n">
+      <c r="T115" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16871,11 +16615,11 @@
       <c r="S116" t="b">
         <v>0</v>
       </c>
-      <c r="T116" s="2" t="n">
+      <c r="T116" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -17004,11 +16748,11 @@
       <c r="S117" t="b">
         <v>0</v>
       </c>
-      <c r="T117" s="2" t="n">
+      <c r="T117" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -17137,11 +16881,11 @@
       <c r="S118" t="b">
         <v>0</v>
       </c>
-      <c r="T118" s="2" t="n">
+      <c r="T118" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17270,11 +17014,11 @@
       <c r="S119" t="b">
         <v>0</v>
       </c>
-      <c r="T119" s="2" t="n">
+      <c r="T119" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17403,11 +17147,11 @@
       <c r="S120" t="b">
         <v>0</v>
       </c>
-      <c r="T120" s="2" t="n">
+      <c r="T120" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17536,11 +17280,11 @@
       <c r="S121" t="b">
         <v>0</v>
       </c>
-      <c r="T121" s="2" t="n">
+      <c r="T121" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17669,11 +17413,11 @@
       <c r="S122" t="b">
         <v>0</v>
       </c>
-      <c r="T122" s="2" t="n">
+      <c r="T122" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17802,11 +17546,11 @@
       <c r="S123" t="b">
         <v>0</v>
       </c>
-      <c r="T123" s="2" t="n">
+      <c r="T123" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17935,11 +17679,11 @@
       <c r="S124" t="b">
         <v>0</v>
       </c>
-      <c r="T124" s="2" t="n">
+      <c r="T124" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -18068,11 +17812,11 @@
       <c r="S125" t="b">
         <v>0</v>
       </c>
-      <c r="T125" s="2" t="n">
+      <c r="T125" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -18201,11 +17945,11 @@
       <c r="S126" t="b">
         <v>0</v>
       </c>
-      <c r="T126" s="2" t="n">
+      <c r="T126" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18334,11 +18078,11 @@
       <c r="S127" t="b">
         <v>0</v>
       </c>
-      <c r="T127" s="2" t="n">
+      <c r="T127" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18467,11 +18211,11 @@
       <c r="S128" t="b">
         <v>0</v>
       </c>
-      <c r="T128" s="2" t="n">
+      <c r="T128" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18600,11 +18344,11 @@
       <c r="S129" t="b">
         <v>0</v>
       </c>
-      <c r="T129" s="2" t="n">
+      <c r="T129" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18733,11 +18477,11 @@
       <c r="S130" t="b">
         <v>0</v>
       </c>
-      <c r="T130" s="2" t="n">
+      <c r="T130" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18866,11 +18610,11 @@
       <c r="S131" t="b">
         <v>0</v>
       </c>
-      <c r="T131" s="2" t="n">
+      <c r="T131" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18999,11 +18743,11 @@
       <c r="S132" t="b">
         <v>0</v>
       </c>
-      <c r="T132" s="2" t="n">
+      <c r="T132" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -19132,11 +18876,11 @@
       <c r="S133" t="b">
         <v>0</v>
       </c>
-      <c r="T133" s="2" t="n">
+      <c r="T133" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19265,11 +19009,11 @@
       <c r="S134" t="b">
         <v>0</v>
       </c>
-      <c r="T134" s="2" t="n">
+      <c r="T134" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19398,11 +19142,11 @@
       <c r="S135" t="b">
         <v>0</v>
       </c>
-      <c r="T135" s="2" t="n">
+      <c r="T135" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19531,11 +19275,11 @@
       <c r="S136" t="b">
         <v>0</v>
       </c>
-      <c r="T136" s="2" t="n">
+      <c r="T136" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19664,11 +19408,11 @@
       <c r="S137" t="b">
         <v>0</v>
       </c>
-      <c r="T137" s="2" t="n">
+      <c r="T137" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19797,11 +19541,11 @@
       <c r="S138" t="b">
         <v>0</v>
       </c>
-      <c r="T138" s="2" t="n">
+      <c r="T138" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19930,11 +19674,11 @@
       <c r="S139" t="b">
         <v>0</v>
       </c>
-      <c r="T139" s="2" t="n">
+      <c r="T139" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -20063,11 +19807,11 @@
       <c r="S140" t="b">
         <v>0</v>
       </c>
-      <c r="T140" s="2" t="n">
+      <c r="T140" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -20196,11 +19940,11 @@
       <c r="S141" t="b">
         <v>0</v>
       </c>
-      <c r="T141" s="2" t="n">
+      <c r="T141" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20329,11 +20073,11 @@
       <c r="S142" t="b">
         <v>0</v>
       </c>
-      <c r="T142" s="2" t="n">
+      <c r="T142" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20462,11 +20206,11 @@
       <c r="S143" t="b">
         <v>0</v>
       </c>
-      <c r="T143" s="2" t="n">
+      <c r="T143" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20595,11 +20339,11 @@
       <c r="S144" t="b">
         <v>0</v>
       </c>
-      <c r="T144" s="2" t="n">
+      <c r="T144" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20728,11 +20472,11 @@
       <c r="S145" t="b">
         <v>0</v>
       </c>
-      <c r="T145" s="2" t="n">
+      <c r="T145" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20861,11 +20605,11 @@
       <c r="S146" t="b">
         <v>0</v>
       </c>
-      <c r="T146" s="2" t="n">
+      <c r="T146" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20994,11 +20738,11 @@
       <c r="S147" t="b">
         <v>0</v>
       </c>
-      <c r="T147" s="2" t="n">
+      <c r="T147" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -21127,11 +20871,11 @@
       <c r="S148" t="b">
         <v>0</v>
       </c>
-      <c r="T148" s="2" t="n">
+      <c r="T148" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21260,11 +21004,11 @@
       <c r="S149" t="b">
         <v>0</v>
       </c>
-      <c r="T149" s="2" t="n">
+      <c r="T149" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21393,11 +21137,11 @@
       <c r="S150" t="b">
         <v>0</v>
       </c>
-      <c r="T150" s="2" t="n">
+      <c r="T150" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21526,11 +21270,11 @@
       <c r="S151" t="b">
         <v>0</v>
       </c>
-      <c r="T151" s="2" t="n">
+      <c r="T151" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21659,11 +21403,11 @@
       <c r="S152" t="b">
         <v>0</v>
       </c>
-      <c r="T152" s="2" t="n">
+      <c r="T152" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21792,11 +21536,11 @@
       <c r="S153" t="b">
         <v>0</v>
       </c>
-      <c r="T153" s="2" t="n">
+      <c r="T153" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21925,11 +21669,11 @@
       <c r="S154" t="b">
         <v>0</v>
       </c>
-      <c r="T154" s="2" t="n">
+      <c r="T154" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -22058,11 +21802,11 @@
       <c r="S155" t="b">
         <v>0</v>
       </c>
-      <c r="T155" s="2" t="n">
+      <c r="T155" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -22191,11 +21935,11 @@
       <c r="S156" t="b">
         <v>0</v>
       </c>
-      <c r="T156" s="2" t="n">
+      <c r="T156" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22324,11 +22068,11 @@
       <c r="S157" t="b">
         <v>0</v>
       </c>
-      <c r="T157" s="2" t="n">
+      <c r="T157" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22457,11 +22201,11 @@
       <c r="S158" t="b">
         <v>0</v>
       </c>
-      <c r="T158" s="2" t="n">
+      <c r="T158" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22590,11 +22334,11 @@
       <c r="S159" t="b">
         <v>0</v>
       </c>
-      <c r="T159" s="2" t="n">
+      <c r="T159" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22723,11 +22467,11 @@
       <c r="S160" t="b">
         <v>0</v>
       </c>
-      <c r="T160" s="2" t="n">
+      <c r="T160" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22856,11 +22600,11 @@
       <c r="S161" t="b">
         <v>0</v>
       </c>
-      <c r="T161" s="2" t="n">
+      <c r="T161" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22989,11 +22733,11 @@
       <c r="S162" t="b">
         <v>0</v>
       </c>
-      <c r="T162" s="2" t="n">
+      <c r="T162" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -23122,11 +22866,11 @@
       <c r="S163" t="b">
         <v>0</v>
       </c>
-      <c r="T163" s="2" t="n">
+      <c r="T163" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23255,11 +22999,11 @@
       <c r="S164" t="b">
         <v>0</v>
       </c>
-      <c r="T164" s="2" t="n">
+      <c r="T164" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23388,11 +23132,11 @@
       <c r="S165" t="b">
         <v>0</v>
       </c>
-      <c r="T165" s="2" t="n">
+      <c r="T165" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23521,11 +23265,11 @@
       <c r="S166" t="b">
         <v>0</v>
       </c>
-      <c r="T166" s="2" t="n">
+      <c r="T166" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23654,11 +23398,11 @@
       <c r="S167" t="b">
         <v>0</v>
       </c>
-      <c r="T167" s="2" t="n">
+      <c r="T167" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23787,11 +23531,11 @@
       <c r="S168" t="b">
         <v>0</v>
       </c>
-      <c r="T168" s="2" t="n">
+      <c r="T168" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23920,11 +23664,11 @@
       <c r="S169" t="b">
         <v>0</v>
       </c>
-      <c r="T169" s="2" t="n">
+      <c r="T169" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -24053,11 +23797,11 @@
       <c r="S170" t="b">
         <v>0</v>
       </c>
-      <c r="T170" s="2" t="n">
+      <c r="T170" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -24186,11 +23930,11 @@
       <c r="S171" t="b">
         <v>0</v>
       </c>
-      <c r="T171" s="2" t="n">
+      <c r="T171" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24319,11 +24063,11 @@
       <c r="S172" t="b">
         <v>0</v>
       </c>
-      <c r="T172" s="2" t="n">
+      <c r="T172" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24452,11 +24196,11 @@
       <c r="S173" t="b">
         <v>0</v>
       </c>
-      <c r="T173" s="2" t="n">
+      <c r="T173" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24585,11 +24329,11 @@
       <c r="S174" t="b">
         <v>0</v>
       </c>
-      <c r="T174" s="2" t="n">
+      <c r="T174" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24718,11 +24462,11 @@
       <c r="S175" t="b">
         <v>0</v>
       </c>
-      <c r="T175" s="2" t="n">
+      <c r="T175" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24851,11 +24595,11 @@
       <c r="S176" t="b">
         <v>0</v>
       </c>
-      <c r="T176" s="2" t="n">
+      <c r="T176" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24984,11 +24728,11 @@
       <c r="S177" t="b">
         <v>0</v>
       </c>
-      <c r="T177" s="2" t="n">
+      <c r="T177" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -25117,11 +24861,11 @@
       <c r="S178" t="b">
         <v>0</v>
       </c>
-      <c r="T178" s="2" t="n">
+      <c r="T178" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -25250,11 +24994,11 @@
       <c r="S179" t="b">
         <v>0</v>
       </c>
-      <c r="T179" s="2" t="n">
+      <c r="T179" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25383,11 +25127,11 @@
       <c r="S180" t="b">
         <v>0</v>
       </c>
-      <c r="T180" s="2" t="n">
+      <c r="T180" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25516,11 +25260,11 @@
       <c r="S181" t="b">
         <v>0</v>
       </c>
-      <c r="T181" s="2" t="n">
+      <c r="T181" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25649,11 +25393,11 @@
       <c r="S182" t="b">
         <v>0</v>
       </c>
-      <c r="T182" s="2" t="n">
+      <c r="T182" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25782,11 +25526,11 @@
       <c r="S183" t="b">
         <v>0</v>
       </c>
-      <c r="T183" s="2" t="n">
+      <c r="T183" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25915,11 +25659,11 @@
       <c r="S184" t="b">
         <v>0</v>
       </c>
-      <c r="T184" s="2" t="n">
+      <c r="T184" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -26048,11 +25792,11 @@
       <c r="S185" t="b">
         <v>0</v>
       </c>
-      <c r="T185" s="2" t="n">
+      <c r="T185" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -26181,11 +25925,11 @@
       <c r="S186" t="b">
         <v>0</v>
       </c>
-      <c r="T186" s="2" t="n">
+      <c r="T186" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26314,11 +26058,11 @@
       <c r="S187" t="b">
         <v>0</v>
       </c>
-      <c r="T187" s="2" t="n">
+      <c r="T187" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26447,11 +26191,11 @@
       <c r="S188" t="b">
         <v>0</v>
       </c>
-      <c r="T188" s="2" t="n">
+      <c r="T188" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26580,11 +26324,11 @@
       <c r="S189" t="b">
         <v>0</v>
       </c>
-      <c r="T189" s="2" t="n">
+      <c r="T189" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26713,11 +26457,11 @@
       <c r="S190" t="b">
         <v>0</v>
       </c>
-      <c r="T190" s="2" t="n">
+      <c r="T190" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26846,11 +26590,11 @@
       <c r="S191" t="b">
         <v>0</v>
       </c>
-      <c r="T191" s="2" t="n">
+      <c r="T191" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>
@@ -26893,6 +26637,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="By Customer" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Aging" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Daily Trend" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Open Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Customer" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aging" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Trend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,13 +24,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -425,12 +437,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -491,27 +503,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>open_shipments</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_outstanding</t>
         </is>
@@ -877,12 +889,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>aging_bucket</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
@@ -943,19 +955,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>collected</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="B2" t="n">
@@ -963,7 +975,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B3" t="n">
@@ -971,7 +983,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="B4" t="n">
@@ -979,7 +991,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46138</v>
       </c>
       <c r="B5" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="B6" t="n">
@@ -995,7 +1007,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="B7" t="n">
@@ -1003,7 +1015,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="B8" t="n">
@@ -1011,7 +1023,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B9" t="n">
@@ -1019,7 +1031,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B10" t="n">
@@ -1027,7 +1039,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46144</v>
       </c>
       <c r="B11" t="n">
@@ -1035,7 +1047,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46145</v>
       </c>
       <c r="B12" t="n">
@@ -1043,7 +1055,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="B13" t="n">
@@ -1051,7 +1063,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="B14" t="n">
@@ -1059,7 +1071,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="B15" t="n">
@@ -1067,7 +1079,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="B16" t="n">
@@ -1075,7 +1087,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B17" t="n">
@@ -1083,7 +1095,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46151</v>
       </c>
       <c r="B18" t="n">
@@ -1091,7 +1103,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46152</v>
       </c>
       <c r="B19" t="n">
@@ -1099,7 +1111,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B20" t="n">
@@ -1107,7 +1119,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="B21" t="n">
@@ -1115,7 +1127,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="B22" t="n">
@@ -1123,7 +1135,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46156</v>
       </c>
       <c r="B23" t="n">
@@ -1131,7 +1143,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B24" t="n">
@@ -1139,7 +1151,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46158</v>
       </c>
       <c r="B25" t="n">
@@ -1147,7 +1159,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46159</v>
       </c>
       <c r="B26" t="n">
@@ -1155,7 +1167,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B27" t="n">
@@ -1163,7 +1175,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="B28" t="n">
@@ -1171,7 +1183,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="B29" t="n">
@@ -1179,7 +1191,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="B30" t="n">
@@ -1187,7 +1199,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B31" t="n">
@@ -1209,157 +1221,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>shipment_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>material_category</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>material_name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>quantity_mt</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>rate_per_mt</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sale_value_without_gst</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gst_rate_pct</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>gst_amount</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>invoice_amount</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>shipment_date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>delivered_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>invoice_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>vehicle_number</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>sales_order_id</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>amount_paid_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>outstanding</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>is_settled</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>due_date_parsed</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>days_to_due</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>days_overdue</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>eligible_for_reminder</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>eligible_for_overdue</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>in_7d_window</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>in_3d_window</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>in_1d_window</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>aging_bucket</t>
         </is>
@@ -1453,7 +1465,7 @@
       <c r="S2" t="b">
         <v>0</v>
       </c>
-      <c r="T2" s="1" t="n">
+      <c r="T2" s="2" t="n">
         <v>46095</v>
       </c>
       <c r="U2" t="n">
@@ -1586,7 +1598,7 @@
       <c r="S3" t="b">
         <v>0</v>
       </c>
-      <c r="T3" s="1" t="n">
+      <c r="T3" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="U3" t="n">
@@ -1719,7 +1731,7 @@
       <c r="S4" t="b">
         <v>0</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="T4" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="U4" t="n">
@@ -1852,7 +1864,7 @@
       <c r="S5" t="b">
         <v>0</v>
       </c>
-      <c r="T5" s="1" t="n">
+      <c r="T5" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="U5" t="n">
@@ -1985,7 +1997,7 @@
       <c r="S6" t="b">
         <v>0</v>
       </c>
-      <c r="T6" s="1" t="n">
+      <c r="T6" s="2" t="n">
         <v>46124</v>
       </c>
       <c r="U6" t="n">
@@ -2118,7 +2130,7 @@
       <c r="S7" t="b">
         <v>0</v>
       </c>
-      <c r="T7" s="1" t="n">
+      <c r="T7" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="U7" t="n">
@@ -2251,7 +2263,7 @@
       <c r="S8" t="b">
         <v>0</v>
       </c>
-      <c r="T8" s="1" t="n">
+      <c r="T8" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="U8" t="n">
@@ -2384,7 +2396,7 @@
       <c r="S9" t="b">
         <v>0</v>
       </c>
-      <c r="T9" s="1" t="n">
+      <c r="T9" s="2" t="n">
         <v>46169</v>
       </c>
       <c r="U9" t="n">
@@ -2517,7 +2529,7 @@
       <c r="S10" t="b">
         <v>0</v>
       </c>
-      <c r="T10" s="1" t="n">
+      <c r="T10" s="2" t="n">
         <v>46172</v>
       </c>
       <c r="U10" t="n">
@@ -2650,7 +2662,7 @@
       <c r="S11" t="b">
         <v>0</v>
       </c>
-      <c r="T11" s="1" t="n">
+      <c r="T11" s="2" t="n">
         <v>46172</v>
       </c>
       <c r="U11" t="n">
@@ -2783,7 +2795,7 @@
       <c r="S12" t="b">
         <v>0</v>
       </c>
-      <c r="T12" s="1" t="n">
+      <c r="T12" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="U12" t="n">
@@ -2916,7 +2928,7 @@
       <c r="S13" t="b">
         <v>0</v>
       </c>
-      <c r="T13" s="1" t="n">
+      <c r="T13" s="2" t="n">
         <v>46163</v>
       </c>
       <c r="U13" t="n">
@@ -3049,7 +3061,7 @@
       <c r="S14" t="b">
         <v>0</v>
       </c>
-      <c r="T14" s="1" t="n">
+      <c r="T14" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="U14" t="n">
@@ -3182,7 +3194,7 @@
       <c r="S15" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="1" t="n">
+      <c r="T15" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="U15" t="n">
@@ -3315,7 +3327,7 @@
       <c r="S16" t="b">
         <v>0</v>
       </c>
-      <c r="T16" s="1" t="n">
+      <c r="T16" s="2" t="n">
         <v>46186</v>
       </c>
       <c r="U16" t="n">
@@ -3448,7 +3460,7 @@
       <c r="S17" t="b">
         <v>0</v>
       </c>
-      <c r="T17" s="1" t="n">
+      <c r="T17" s="2" t="n">
         <v>46187</v>
       </c>
       <c r="U17" t="n">
@@ -3581,7 +3593,7 @@
       <c r="S18" t="b">
         <v>0</v>
       </c>
-      <c r="T18" s="1" t="n">
+      <c r="T18" s="2" t="n">
         <v>46189</v>
       </c>
       <c r="U18" t="n">
@@ -3714,7 +3726,7 @@
       <c r="S19" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="1" t="n">
+      <c r="T19" s="2" t="n">
         <v>46189</v>
       </c>
       <c r="U19" t="n">
@@ -3847,7 +3859,7 @@
       <c r="S20" t="b">
         <v>0</v>
       </c>
-      <c r="T20" s="1" t="n">
+      <c r="T20" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U20" t="n">
@@ -3980,7 +3992,7 @@
       <c r="S21" t="b">
         <v>0</v>
       </c>
-      <c r="T21" s="1" t="n">
+      <c r="T21" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U21" t="n">
@@ -4113,7 +4125,7 @@
       <c r="S22" t="b">
         <v>0</v>
       </c>
-      <c r="T22" s="1" t="n">
+      <c r="T22" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U22" t="n">
@@ -4246,7 +4258,7 @@
       <c r="S23" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="1" t="n">
+      <c r="T23" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="U23" t="n">
@@ -4379,7 +4391,7 @@
       <c r="S24" t="b">
         <v>0</v>
       </c>
-      <c r="T24" s="1" t="n">
+      <c r="T24" s="2" t="n">
         <v>46194</v>
       </c>
       <c r="U24" t="n">
@@ -4512,7 +4524,7 @@
       <c r="S25" t="b">
         <v>0</v>
       </c>
-      <c r="T25" s="1" t="n">
+      <c r="T25" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="U25" t="n">
@@ -4645,7 +4657,7 @@
       <c r="S26" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="1" t="n">
+      <c r="T26" s="2" t="n">
         <v>46180</v>
       </c>
       <c r="U26" t="n">
@@ -4778,7 +4790,7 @@
       <c r="S27" t="b">
         <v>0</v>
       </c>
-      <c r="T27" s="1" t="n">
+      <c r="T27" s="2" t="n">
         <v>46196</v>
       </c>
       <c r="U27" t="n">
@@ -4911,7 +4923,7 @@
       <c r="S28" t="b">
         <v>0</v>
       </c>
-      <c r="T28" s="1" t="n">
+      <c r="T28" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="U28" t="n">
@@ -5044,7 +5056,7 @@
       <c r="S29" t="b">
         <v>0</v>
       </c>
-      <c r="T29" s="1" t="n">
+      <c r="T29" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="U29" t="n">
@@ -5177,7 +5189,7 @@
       <c r="S30" t="b">
         <v>0</v>
       </c>
-      <c r="T30" s="1" t="n">
+      <c r="T30" s="2" t="n">
         <v>46197</v>
       </c>
       <c r="U30" t="n">
@@ -5310,7 +5322,7 @@
       <c r="S31" t="b">
         <v>0</v>
       </c>
-      <c r="T31" s="1" t="n">
+      <c r="T31" s="2" t="n">
         <v>46197</v>
       </c>
       <c r="U31" t="n">
@@ -5443,7 +5455,7 @@
       <c r="S32" t="b">
         <v>0</v>
       </c>
-      <c r="T32" s="1" t="n">
+      <c r="T32" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U32" t="n">
@@ -5576,7 +5588,7 @@
       <c r="S33" t="b">
         <v>0</v>
       </c>
-      <c r="T33" s="1" t="n">
+      <c r="T33" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U33" t="n">
@@ -5709,7 +5721,7 @@
       <c r="S34" t="b">
         <v>0</v>
       </c>
-      <c r="T34" s="1" t="n">
+      <c r="T34" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U34" t="n">
@@ -5842,7 +5854,7 @@
       <c r="S35" t="b">
         <v>0</v>
       </c>
-      <c r="T35" s="1" t="n">
+      <c r="T35" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U35" t="n">
@@ -5975,7 +5987,7 @@
       <c r="S36" t="b">
         <v>0</v>
       </c>
-      <c r="T36" s="1" t="n">
+      <c r="T36" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U36" t="n">
@@ -6108,7 +6120,7 @@
       <c r="S37" t="b">
         <v>0</v>
       </c>
-      <c r="T37" s="1" t="n">
+      <c r="T37" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U37" t="n">
@@ -6241,7 +6253,7 @@
       <c r="S38" t="b">
         <v>0</v>
       </c>
-      <c r="T38" s="1" t="n">
+      <c r="T38" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U38" t="n">
@@ -6374,7 +6386,7 @@
       <c r="S39" t="b">
         <v>0</v>
       </c>
-      <c r="T39" s="1" t="n">
+      <c r="T39" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U39" t="n">
@@ -6507,7 +6519,7 @@
       <c r="S40" t="b">
         <v>0</v>
       </c>
-      <c r="T40" s="1" t="n">
+      <c r="T40" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U40" t="n">
@@ -6640,7 +6652,7 @@
       <c r="S41" t="b">
         <v>0</v>
       </c>
-      <c r="T41" s="1" t="n">
+      <c r="T41" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U41" t="n">
@@ -6773,7 +6785,7 @@
       <c r="S42" t="b">
         <v>0</v>
       </c>
-      <c r="T42" s="1" t="n">
+      <c r="T42" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U42" t="n">
@@ -6906,7 +6918,7 @@
       <c r="S43" t="b">
         <v>0</v>
       </c>
-      <c r="T43" s="1" t="n">
+      <c r="T43" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U43" t="n">
@@ -7039,7 +7051,7 @@
       <c r="S44" t="b">
         <v>0</v>
       </c>
-      <c r="T44" s="1" t="n">
+      <c r="T44" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U44" t="n">
@@ -7172,7 +7184,7 @@
       <c r="S45" t="b">
         <v>0</v>
       </c>
-      <c r="T45" s="1" t="n">
+      <c r="T45" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U45" t="n">
@@ -7305,7 +7317,7 @@
       <c r="S46" t="b">
         <v>0</v>
       </c>
-      <c r="T46" s="1" t="n">
+      <c r="T46" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U46" t="n">
@@ -7438,7 +7450,7 @@
       <c r="S47" t="b">
         <v>0</v>
       </c>
-      <c r="T47" s="1" t="n">
+      <c r="T47" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U47" t="n">
@@ -7571,7 +7583,7 @@
       <c r="S48" t="b">
         <v>0</v>
       </c>
-      <c r="T48" s="1" t="n">
+      <c r="T48" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U48" t="n">
@@ -7704,7 +7716,7 @@
       <c r="S49" t="b">
         <v>0</v>
       </c>
-      <c r="T49" s="1" t="n">
+      <c r="T49" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U49" t="n">
@@ -7837,7 +7849,7 @@
       <c r="S50" t="b">
         <v>0</v>
       </c>
-      <c r="T50" s="1" t="n">
+      <c r="T50" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U50" t="n">
@@ -7970,7 +7982,7 @@
       <c r="S51" t="b">
         <v>0</v>
       </c>
-      <c r="T51" s="1" t="n">
+      <c r="T51" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U51" t="n">
@@ -8103,7 +8115,7 @@
       <c r="S52" t="b">
         <v>0</v>
       </c>
-      <c r="T52" s="1" t="n">
+      <c r="T52" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U52" t="n">
@@ -8236,7 +8248,7 @@
       <c r="S53" t="b">
         <v>0</v>
       </c>
-      <c r="T53" s="1" t="n">
+      <c r="T53" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U53" t="n">
@@ -8369,7 +8381,7 @@
       <c r="S54" t="b">
         <v>0</v>
       </c>
-      <c r="T54" s="1" t="n">
+      <c r="T54" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U54" t="n">
@@ -8502,7 +8514,7 @@
       <c r="S55" t="b">
         <v>0</v>
       </c>
-      <c r="T55" s="1" t="n">
+      <c r="T55" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U55" t="n">
@@ -8635,7 +8647,7 @@
       <c r="S56" t="b">
         <v>0</v>
       </c>
-      <c r="T56" s="1" t="n">
+      <c r="T56" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U56" t="n">
@@ -8768,7 +8780,7 @@
       <c r="S57" t="b">
         <v>0</v>
       </c>
-      <c r="T57" s="1" t="n">
+      <c r="T57" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U57" t="n">
@@ -8901,7 +8913,7 @@
       <c r="S58" t="b">
         <v>0</v>
       </c>
-      <c r="T58" s="1" t="n">
+      <c r="T58" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U58" t="n">
@@ -9034,7 +9046,7 @@
       <c r="S59" t="b">
         <v>0</v>
       </c>
-      <c r="T59" s="1" t="n">
+      <c r="T59" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U59" t="n">
@@ -9167,7 +9179,7 @@
       <c r="S60" t="b">
         <v>0</v>
       </c>
-      <c r="T60" s="1" t="n">
+      <c r="T60" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U60" t="n">
@@ -9300,7 +9312,7 @@
       <c r="S61" t="b">
         <v>0</v>
       </c>
-      <c r="T61" s="1" t="n">
+      <c r="T61" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U61" t="n">
@@ -9433,7 +9445,7 @@
       <c r="S62" t="b">
         <v>0</v>
       </c>
-      <c r="T62" s="1" t="n">
+      <c r="T62" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U62" t="n">
@@ -9566,7 +9578,7 @@
       <c r="S63" t="b">
         <v>0</v>
       </c>
-      <c r="T63" s="1" t="n">
+      <c r="T63" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U63" t="n">
@@ -9699,7 +9711,7 @@
       <c r="S64" t="b">
         <v>0</v>
       </c>
-      <c r="T64" s="1" t="n">
+      <c r="T64" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U64" t="n">
@@ -9832,7 +9844,7 @@
       <c r="S65" t="b">
         <v>0</v>
       </c>
-      <c r="T65" s="1" t="n">
+      <c r="T65" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U65" t="n">
@@ -9965,7 +9977,7 @@
       <c r="S66" t="b">
         <v>0</v>
       </c>
-      <c r="T66" s="1" t="n">
+      <c r="T66" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U66" t="n">
@@ -10098,7 +10110,7 @@
       <c r="S67" t="b">
         <v>0</v>
       </c>
-      <c r="T67" s="1" t="n">
+      <c r="T67" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U67" t="n">
@@ -10231,7 +10243,7 @@
       <c r="S68" t="b">
         <v>0</v>
       </c>
-      <c r="T68" s="1" t="n">
+      <c r="T68" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U68" t="n">
@@ -10364,7 +10376,7 @@
       <c r="S69" t="b">
         <v>0</v>
       </c>
-      <c r="T69" s="1" t="n">
+      <c r="T69" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U69" t="n">
@@ -10497,7 +10509,7 @@
       <c r="S70" t="b">
         <v>0</v>
       </c>
-      <c r="T70" s="1" t="n">
+      <c r="T70" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U70" t="n">
@@ -10630,7 +10642,7 @@
       <c r="S71" t="b">
         <v>0</v>
       </c>
-      <c r="T71" s="1" t="n">
+      <c r="T71" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U71" t="n">
@@ -10763,7 +10775,7 @@
       <c r="S72" t="b">
         <v>0</v>
       </c>
-      <c r="T72" s="1" t="n">
+      <c r="T72" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U72" t="n">
@@ -10896,7 +10908,7 @@
       <c r="S73" t="b">
         <v>0</v>
       </c>
-      <c r="T73" s="1" t="n">
+      <c r="T73" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U73" t="n">
@@ -11029,7 +11041,7 @@
       <c r="S74" t="b">
         <v>0</v>
       </c>
-      <c r="T74" s="1" t="n">
+      <c r="T74" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U74" t="n">
@@ -11162,7 +11174,7 @@
       <c r="S75" t="b">
         <v>0</v>
       </c>
-      <c r="T75" s="1" t="n">
+      <c r="T75" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U75" t="n">
@@ -11295,7 +11307,7 @@
       <c r="S76" t="b">
         <v>0</v>
       </c>
-      <c r="T76" s="1" t="n">
+      <c r="T76" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U76" t="n">
@@ -11428,7 +11440,7 @@
       <c r="S77" t="b">
         <v>0</v>
       </c>
-      <c r="T77" s="1" t="n">
+      <c r="T77" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U77" t="n">
@@ -11561,7 +11573,7 @@
       <c r="S78" t="b">
         <v>0</v>
       </c>
-      <c r="T78" s="1" t="n">
+      <c r="T78" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U78" t="n">
@@ -11694,7 +11706,7 @@
       <c r="S79" t="b">
         <v>0</v>
       </c>
-      <c r="T79" s="1" t="n">
+      <c r="T79" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U79" t="n">
@@ -11827,7 +11839,7 @@
       <c r="S80" t="b">
         <v>0</v>
       </c>
-      <c r="T80" s="1" t="n">
+      <c r="T80" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U80" t="n">
@@ -11960,7 +11972,7 @@
       <c r="S81" t="b">
         <v>0</v>
       </c>
-      <c r="T81" s="1" t="n">
+      <c r="T81" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U81" t="n">
@@ -12093,7 +12105,7 @@
       <c r="S82" t="b">
         <v>0</v>
       </c>
-      <c r="T82" s="1" t="n">
+      <c r="T82" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U82" t="n">
@@ -12226,7 +12238,7 @@
       <c r="S83" t="b">
         <v>0</v>
       </c>
-      <c r="T83" s="1" t="n">
+      <c r="T83" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U83" t="n">
@@ -12359,7 +12371,7 @@
       <c r="S84" t="b">
         <v>0</v>
       </c>
-      <c r="T84" s="1" t="n">
+      <c r="T84" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="U84" t="n">
@@ -12492,7 +12504,7 @@
       <c r="S85" t="b">
         <v>0</v>
       </c>
-      <c r="T85" s="1" t="n">
+      <c r="T85" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="U85" t="n">
@@ -12625,7 +12637,7 @@
       <c r="S86" t="b">
         <v>0</v>
       </c>
-      <c r="T86" s="1" t="n">
+      <c r="T86" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U86" t="n">
@@ -12758,7 +12770,7 @@
       <c r="S87" t="b">
         <v>0</v>
       </c>
-      <c r="T87" s="1" t="n">
+      <c r="T87" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U87" t="n">
@@ -12891,7 +12903,7 @@
       <c r="S88" t="b">
         <v>0</v>
       </c>
-      <c r="T88" s="1" t="n">
+      <c r="T88" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U88" t="n">
@@ -13024,7 +13036,7 @@
       <c r="S89" t="b">
         <v>0</v>
       </c>
-      <c r="T89" s="1" t="n">
+      <c r="T89" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U89" t="n">
@@ -13157,7 +13169,7 @@
       <c r="S90" t="b">
         <v>0</v>
       </c>
-      <c r="T90" s="1" t="n">
+      <c r="T90" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U90" t="n">
@@ -13290,7 +13302,7 @@
       <c r="S91" t="b">
         <v>0</v>
       </c>
-      <c r="T91" s="1" t="n">
+      <c r="T91" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U91" t="n">
@@ -13423,7 +13435,7 @@
       <c r="S92" t="b">
         <v>0</v>
       </c>
-      <c r="T92" s="1" t="n">
+      <c r="T92" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U92" t="n">
@@ -13556,7 +13568,7 @@
       <c r="S93" t="b">
         <v>0</v>
       </c>
-      <c r="T93" s="1" t="n">
+      <c r="T93" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U93" t="n">
@@ -13689,7 +13701,7 @@
       <c r="S94" t="b">
         <v>0</v>
       </c>
-      <c r="T94" s="1" t="n">
+      <c r="T94" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U94" t="n">
@@ -13822,7 +13834,7 @@
       <c r="S95" t="b">
         <v>0</v>
       </c>
-      <c r="T95" s="1" t="n">
+      <c r="T95" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U95" t="n">
@@ -13955,7 +13967,7 @@
       <c r="S96" t="b">
         <v>0</v>
       </c>
-      <c r="T96" s="1" t="n">
+      <c r="T96" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U96" t="n">
@@ -14088,7 +14100,7 @@
       <c r="S97" t="b">
         <v>0</v>
       </c>
-      <c r="T97" s="1" t="n">
+      <c r="T97" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U97" t="n">
@@ -14221,7 +14233,7 @@
       <c r="S98" t="b">
         <v>0</v>
       </c>
-      <c r="T98" s="1" t="n">
+      <c r="T98" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U98" t="n">
@@ -14354,7 +14366,7 @@
       <c r="S99" t="b">
         <v>0</v>
       </c>
-      <c r="T99" s="1" t="n">
+      <c r="T99" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U99" t="n">
@@ -14487,7 +14499,7 @@
       <c r="S100" t="b">
         <v>0</v>
       </c>
-      <c r="T100" s="1" t="n">
+      <c r="T100" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U100" t="n">
@@ -14620,7 +14632,7 @@
       <c r="S101" t="b">
         <v>0</v>
       </c>
-      <c r="T101" s="1" t="n">
+      <c r="T101" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U101" t="n">
@@ -14753,7 +14765,7 @@
       <c r="S102" t="b">
         <v>0</v>
       </c>
-      <c r="T102" s="1" t="n">
+      <c r="T102" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U102" t="n">
@@ -14886,7 +14898,7 @@
       <c r="S103" t="b">
         <v>0</v>
       </c>
-      <c r="T103" s="1" t="n">
+      <c r="T103" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U103" t="n">
@@ -15019,7 +15031,7 @@
       <c r="S104" t="b">
         <v>0</v>
       </c>
-      <c r="T104" s="1" t="n">
+      <c r="T104" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U104" t="n">
@@ -15152,7 +15164,7 @@
       <c r="S105" t="b">
         <v>0</v>
       </c>
-      <c r="T105" s="1" t="n">
+      <c r="T105" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U105" t="n">
@@ -15285,7 +15297,7 @@
       <c r="S106" t="b">
         <v>0</v>
       </c>
-      <c r="T106" s="1" t="n">
+      <c r="T106" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U106" t="n">
@@ -15418,7 +15430,7 @@
       <c r="S107" t="b">
         <v>0</v>
       </c>
-      <c r="T107" s="1" t="n">
+      <c r="T107" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U107" t="n">
@@ -15551,7 +15563,7 @@
       <c r="S108" t="b">
         <v>0</v>
       </c>
-      <c r="T108" s="1" t="n">
+      <c r="T108" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U108" t="n">
@@ -15684,7 +15696,7 @@
       <c r="S109" t="b">
         <v>0</v>
       </c>
-      <c r="T109" s="1" t="n">
+      <c r="T109" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U109" t="n">
@@ -15817,7 +15829,7 @@
       <c r="S110" t="b">
         <v>0</v>
       </c>
-      <c r="T110" s="1" t="n">
+      <c r="T110" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U110" t="n">
@@ -15950,7 +15962,7 @@
       <c r="S111" t="b">
         <v>0</v>
       </c>
-      <c r="T111" s="1" t="n">
+      <c r="T111" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U111" t="n">
@@ -16083,7 +16095,7 @@
       <c r="S112" t="b">
         <v>0</v>
       </c>
-      <c r="T112" s="1" t="n">
+      <c r="T112" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U112" t="n">
@@ -16216,7 +16228,7 @@
       <c r="S113" t="b">
         <v>0</v>
       </c>
-      <c r="T113" s="1" t="n">
+      <c r="T113" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U113" t="n">
@@ -16349,7 +16361,7 @@
       <c r="S114" t="b">
         <v>0</v>
       </c>
-      <c r="T114" s="1" t="n">
+      <c r="T114" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U114" t="n">
@@ -16482,7 +16494,7 @@
       <c r="S115" t="b">
         <v>0</v>
       </c>
-      <c r="T115" s="1" t="n">
+      <c r="T115" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U115" t="n">
@@ -16615,7 +16627,7 @@
       <c r="S116" t="b">
         <v>0</v>
       </c>
-      <c r="T116" s="1" t="n">
+      <c r="T116" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U116" t="n">
@@ -16748,7 +16760,7 @@
       <c r="S117" t="b">
         <v>0</v>
       </c>
-      <c r="T117" s="1" t="n">
+      <c r="T117" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U117" t="n">
@@ -16881,7 +16893,7 @@
       <c r="S118" t="b">
         <v>0</v>
       </c>
-      <c r="T118" s="1" t="n">
+      <c r="T118" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U118" t="n">
@@ -17014,7 +17026,7 @@
       <c r="S119" t="b">
         <v>0</v>
       </c>
-      <c r="T119" s="1" t="n">
+      <c r="T119" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U119" t="n">
@@ -17147,7 +17159,7 @@
       <c r="S120" t="b">
         <v>0</v>
       </c>
-      <c r="T120" s="1" t="n">
+      <c r="T120" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U120" t="n">
@@ -17280,7 +17292,7 @@
       <c r="S121" t="b">
         <v>0</v>
       </c>
-      <c r="T121" s="1" t="n">
+      <c r="T121" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U121" t="n">
@@ -17413,7 +17425,7 @@
       <c r="S122" t="b">
         <v>0</v>
       </c>
-      <c r="T122" s="1" t="n">
+      <c r="T122" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U122" t="n">
@@ -17546,7 +17558,7 @@
       <c r="S123" t="b">
         <v>0</v>
       </c>
-      <c r="T123" s="1" t="n">
+      <c r="T123" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U123" t="n">
@@ -17679,7 +17691,7 @@
       <c r="S124" t="b">
         <v>0</v>
       </c>
-      <c r="T124" s="1" t="n">
+      <c r="T124" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U124" t="n">
@@ -17812,7 +17824,7 @@
       <c r="S125" t="b">
         <v>0</v>
       </c>
-      <c r="T125" s="1" t="n">
+      <c r="T125" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U125" t="n">
@@ -17945,7 +17957,7 @@
       <c r="S126" t="b">
         <v>0</v>
       </c>
-      <c r="T126" s="1" t="n">
+      <c r="T126" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U126" t="n">
@@ -18078,7 +18090,7 @@
       <c r="S127" t="b">
         <v>0</v>
       </c>
-      <c r="T127" s="1" t="n">
+      <c r="T127" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U127" t="n">
@@ -18211,7 +18223,7 @@
       <c r="S128" t="b">
         <v>0</v>
       </c>
-      <c r="T128" s="1" t="n">
+      <c r="T128" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U128" t="n">
@@ -18344,7 +18356,7 @@
       <c r="S129" t="b">
         <v>0</v>
       </c>
-      <c r="T129" s="1" t="n">
+      <c r="T129" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U129" t="n">
@@ -18477,7 +18489,7 @@
       <c r="S130" t="b">
         <v>0</v>
       </c>
-      <c r="T130" s="1" t="n">
+      <c r="T130" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U130" t="n">
@@ -18610,7 +18622,7 @@
       <c r="S131" t="b">
         <v>0</v>
       </c>
-      <c r="T131" s="1" t="n">
+      <c r="T131" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U131" t="n">
@@ -18743,7 +18755,7 @@
       <c r="S132" t="b">
         <v>0</v>
       </c>
-      <c r="T132" s="1" t="n">
+      <c r="T132" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U132" t="n">
@@ -18876,7 +18888,7 @@
       <c r="S133" t="b">
         <v>0</v>
       </c>
-      <c r="T133" s="1" t="n">
+      <c r="T133" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U133" t="n">
@@ -19009,7 +19021,7 @@
       <c r="S134" t="b">
         <v>0</v>
       </c>
-      <c r="T134" s="1" t="n">
+      <c r="T134" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U134" t="n">
@@ -19142,7 +19154,7 @@
       <c r="S135" t="b">
         <v>0</v>
       </c>
-      <c r="T135" s="1" t="n">
+      <c r="T135" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U135" t="n">
@@ -19275,7 +19287,7 @@
       <c r="S136" t="b">
         <v>0</v>
       </c>
-      <c r="T136" s="1" t="n">
+      <c r="T136" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U136" t="n">
@@ -19408,7 +19420,7 @@
       <c r="S137" t="b">
         <v>0</v>
       </c>
-      <c r="T137" s="1" t="n">
+      <c r="T137" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U137" t="n">
@@ -19541,7 +19553,7 @@
       <c r="S138" t="b">
         <v>0</v>
       </c>
-      <c r="T138" s="1" t="n">
+      <c r="T138" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U138" t="n">
@@ -19674,7 +19686,7 @@
       <c r="S139" t="b">
         <v>0</v>
       </c>
-      <c r="T139" s="1" t="n">
+      <c r="T139" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U139" t="n">
@@ -19807,7 +19819,7 @@
       <c r="S140" t="b">
         <v>0</v>
       </c>
-      <c r="T140" s="1" t="n">
+      <c r="T140" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U140" t="n">
@@ -19940,7 +19952,7 @@
       <c r="S141" t="b">
         <v>0</v>
       </c>
-      <c r="T141" s="1" t="n">
+      <c r="T141" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U141" t="n">
@@ -20073,7 +20085,7 @@
       <c r="S142" t="b">
         <v>0</v>
       </c>
-      <c r="T142" s="1" t="n">
+      <c r="T142" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U142" t="n">
@@ -20206,7 +20218,7 @@
       <c r="S143" t="b">
         <v>0</v>
       </c>
-      <c r="T143" s="1" t="n">
+      <c r="T143" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U143" t="n">
@@ -20339,7 +20351,7 @@
       <c r="S144" t="b">
         <v>0</v>
       </c>
-      <c r="T144" s="1" t="n">
+      <c r="T144" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U144" t="n">
@@ -20472,7 +20484,7 @@
       <c r="S145" t="b">
         <v>0</v>
       </c>
-      <c r="T145" s="1" t="n">
+      <c r="T145" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U145" t="n">
@@ -20605,7 +20617,7 @@
       <c r="S146" t="b">
         <v>0</v>
       </c>
-      <c r="T146" s="1" t="n">
+      <c r="T146" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U146" t="n">
@@ -20738,7 +20750,7 @@
       <c r="S147" t="b">
         <v>0</v>
       </c>
-      <c r="T147" s="1" t="n">
+      <c r="T147" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U147" t="n">
@@ -20871,7 +20883,7 @@
       <c r="S148" t="b">
         <v>0</v>
       </c>
-      <c r="T148" s="1" t="n">
+      <c r="T148" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U148" t="n">
@@ -21004,7 +21016,7 @@
       <c r="S149" t="b">
         <v>0</v>
       </c>
-      <c r="T149" s="1" t="n">
+      <c r="T149" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U149" t="n">
@@ -21137,7 +21149,7 @@
       <c r="S150" t="b">
         <v>0</v>
       </c>
-      <c r="T150" s="1" t="n">
+      <c r="T150" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U150" t="n">
@@ -21270,7 +21282,7 @@
       <c r="S151" t="b">
         <v>0</v>
       </c>
-      <c r="T151" s="1" t="n">
+      <c r="T151" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U151" t="n">
@@ -21403,7 +21415,7 @@
       <c r="S152" t="b">
         <v>0</v>
       </c>
-      <c r="T152" s="1" t="n">
+      <c r="T152" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U152" t="n">
@@ -21536,7 +21548,7 @@
       <c r="S153" t="b">
         <v>0</v>
       </c>
-      <c r="T153" s="1" t="n">
+      <c r="T153" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U153" t="n">
@@ -21669,7 +21681,7 @@
       <c r="S154" t="b">
         <v>0</v>
       </c>
-      <c r="T154" s="1" t="n">
+      <c r="T154" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U154" t="n">
@@ -21802,7 +21814,7 @@
       <c r="S155" t="b">
         <v>0</v>
       </c>
-      <c r="T155" s="1" t="n">
+      <c r="T155" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U155" t="n">
@@ -21935,7 +21947,7 @@
       <c r="S156" t="b">
         <v>0</v>
       </c>
-      <c r="T156" s="1" t="n">
+      <c r="T156" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U156" t="n">
@@ -22068,7 +22080,7 @@
       <c r="S157" t="b">
         <v>0</v>
       </c>
-      <c r="T157" s="1" t="n">
+      <c r="T157" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U157" t="n">
@@ -22201,7 +22213,7 @@
       <c r="S158" t="b">
         <v>0</v>
       </c>
-      <c r="T158" s="1" t="n">
+      <c r="T158" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U158" t="n">
@@ -22334,7 +22346,7 @@
       <c r="S159" t="b">
         <v>0</v>
       </c>
-      <c r="T159" s="1" t="n">
+      <c r="T159" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U159" t="n">
@@ -22467,7 +22479,7 @@
       <c r="S160" t="b">
         <v>0</v>
       </c>
-      <c r="T160" s="1" t="n">
+      <c r="T160" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U160" t="n">
@@ -22600,7 +22612,7 @@
       <c r="S161" t="b">
         <v>0</v>
       </c>
-      <c r="T161" s="1" t="n">
+      <c r="T161" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="U161" t="n">
@@ -22733,7 +22745,7 @@
       <c r="S162" t="b">
         <v>0</v>
       </c>
-      <c r="T162" s="1" t="n">
+      <c r="T162" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="U162" t="n">
@@ -22866,7 +22878,7 @@
       <c r="S163" t="b">
         <v>0</v>
       </c>
-      <c r="T163" s="1" t="n">
+      <c r="T163" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U163" t="n">
@@ -22999,7 +23011,7 @@
       <c r="S164" t="b">
         <v>0</v>
       </c>
-      <c r="T164" s="1" t="n">
+      <c r="T164" s="2" t="n">
         <v>46207</v>
       </c>
       <c r="U164" t="n">
@@ -23132,7 +23144,7 @@
       <c r="S165" t="b">
         <v>0</v>
       </c>
-      <c r="T165" s="1" t="n">
+      <c r="T165" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U165" t="n">
@@ -23265,7 +23277,7 @@
       <c r="S166" t="b">
         <v>0</v>
       </c>
-      <c r="T166" s="1" t="n">
+      <c r="T166" s="2" t="n">
         <v>46207</v>
       </c>
       <c r="U166" t="n">
@@ -23398,7 +23410,7 @@
       <c r="S167" t="b">
         <v>0</v>
       </c>
-      <c r="T167" s="1" t="n">
+      <c r="T167" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U167" t="n">
@@ -23531,7 +23543,7 @@
       <c r="S168" t="b">
         <v>0</v>
       </c>
-      <c r="T168" s="1" t="n">
+      <c r="T168" s="2" t="n">
         <v>46207</v>
       </c>
       <c r="U168" t="n">
@@ -23664,7 +23676,7 @@
       <c r="S169" t="b">
         <v>0</v>
       </c>
-      <c r="T169" s="1" t="n">
+      <c r="T169" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U169" t="n">
@@ -23797,7 +23809,7 @@
       <c r="S170" t="b">
         <v>0</v>
       </c>
-      <c r="T170" s="1" t="n">
+      <c r="T170" s="2" t="n">
         <v>46207</v>
       </c>
       <c r="U170" t="n">
@@ -23930,7 +23942,7 @@
       <c r="S171" t="b">
         <v>0</v>
       </c>
-      <c r="T171" s="1" t="n">
+      <c r="T171" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U171" t="n">
@@ -24063,7 +24075,7 @@
       <c r="S172" t="b">
         <v>0</v>
       </c>
-      <c r="T172" s="1" t="n">
+      <c r="T172" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U172" t="n">
@@ -24196,7 +24208,7 @@
       <c r="S173" t="b">
         <v>0</v>
       </c>
-      <c r="T173" s="1" t="n">
+      <c r="T173" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U173" t="n">
@@ -24329,7 +24341,7 @@
       <c r="S174" t="b">
         <v>0</v>
       </c>
-      <c r="T174" s="1" t="n">
+      <c r="T174" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U174" t="n">
@@ -24462,7 +24474,7 @@
       <c r="S175" t="b">
         <v>0</v>
       </c>
-      <c r="T175" s="1" t="n">
+      <c r="T175" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="U175" t="n">
@@ -24595,7 +24607,7 @@
       <c r="S176" t="b">
         <v>0</v>
       </c>
-      <c r="T176" s="1" t="n">
+      <c r="T176" s="2" t="n">
         <v>46207</v>
       </c>
       <c r="U176" t="n">
@@ -24728,7 +24740,7 @@
       <c r="S177" t="b">
         <v>0</v>
       </c>
-      <c r="T177" s="1" t="n">
+      <c r="T177" s="2" t="n">
         <v>46207</v>
       </c>
       <c r="U177" t="n">
@@ -24861,7 +24873,7 @@
       <c r="S178" t="b">
         <v>0</v>
       </c>
-      <c r="T178" s="1" t="n">
+      <c r="T178" s="2" t="n">
         <v>46207</v>
       </c>
       <c r="U178" t="n">
@@ -24994,7 +25006,7 @@
       <c r="S179" t="b">
         <v>0</v>
       </c>
-      <c r="T179" s="1" t="n">
+      <c r="T179" s="2" t="n">
         <v>46193</v>
       </c>
       <c r="U179" t="n">
@@ -25127,7 +25139,7 @@
       <c r="S180" t="b">
         <v>0</v>
       </c>
-      <c r="T180" s="1" t="n">
+      <c r="T180" s="2" t="n">
         <v>46208</v>
       </c>
       <c r="U180" t="n">
@@ -25260,7 +25272,7 @@
       <c r="S181" t="b">
         <v>0</v>
       </c>
-      <c r="T181" s="1" t="n">
+      <c r="T181" s="2" t="n">
         <v>46193</v>
       </c>
       <c r="U181" t="n">
@@ -25393,7 +25405,7 @@
       <c r="S182" t="b">
         <v>0</v>
       </c>
-      <c r="T182" s="1" t="n">
+      <c r="T182" s="2" t="n">
         <v>46193</v>
       </c>
       <c r="U182" t="n">
@@ -25526,7 +25538,7 @@
       <c r="S183" t="b">
         <v>0</v>
       </c>
-      <c r="T183" s="1" t="n">
+      <c r="T183" s="2" t="n">
         <v>46193</v>
       </c>
       <c r="U183" t="n">
@@ -25659,7 +25671,7 @@
       <c r="S184" t="b">
         <v>0</v>
       </c>
-      <c r="T184" s="1" t="n">
+      <c r="T184" s="2" t="n">
         <v>46208</v>
       </c>
       <c r="U184" t="n">
@@ -25792,7 +25804,7 @@
       <c r="S185" t="b">
         <v>0</v>
       </c>
-      <c r="T185" s="1" t="n">
+      <c r="T185" s="2" t="n">
         <v>46193</v>
       </c>
       <c r="U185" t="n">
@@ -25925,7 +25937,7 @@
       <c r="S186" t="b">
         <v>0</v>
       </c>
-      <c r="T186" s="1" t="n">
+      <c r="T186" s="2" t="n">
         <v>46208</v>
       </c>
       <c r="U186" t="n">
@@ -26058,7 +26070,7 @@
       <c r="S187" t="b">
         <v>0</v>
       </c>
-      <c r="T187" s="1" t="n">
+      <c r="T187" s="2" t="n">
         <v>46208</v>
       </c>
       <c r="U187" t="n">
@@ -26191,7 +26203,7 @@
       <c r="S188" t="b">
         <v>0</v>
       </c>
-      <c r="T188" s="1" t="n">
+      <c r="T188" s="2" t="n">
         <v>46208</v>
       </c>
       <c r="U188" t="n">
@@ -26324,7 +26336,7 @@
       <c r="S189" t="b">
         <v>0</v>
       </c>
-      <c r="T189" s="1" t="n">
+      <c r="T189" s="2" t="n">
         <v>46208</v>
       </c>
       <c r="U189" t="n">
@@ -26457,7 +26469,7 @@
       <c r="S190" t="b">
         <v>0</v>
       </c>
-      <c r="T190" s="1" t="n">
+      <c r="T190" s="2" t="n">
         <v>46193</v>
       </c>
       <c r="U190" t="n">
@@ -26590,7 +26602,7 @@
       <c r="S191" t="b">
         <v>0</v>
       </c>
-      <c r="T191" s="1" t="n">
+      <c r="T191" s="2" t="n">
         <v>46193</v>
       </c>
       <c r="U191" t="n">

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Customer" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aging" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Trend" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="KPIs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="By Customer" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aging" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily Trend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,16 +24,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -437,12 +425,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -503,27 +491,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>open_shipments</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>total_outstanding</t>
         </is>
@@ -889,12 +877,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>aging_bucket</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
@@ -955,19 +943,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>collected</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="B2" t="n">
@@ -975,7 +963,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B3" t="n">
@@ -983,7 +971,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46137</v>
       </c>
       <c r="B4" t="n">
@@ -991,7 +979,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46138</v>
       </c>
       <c r="B5" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46139</v>
       </c>
       <c r="B6" t="n">
@@ -1007,7 +995,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46140</v>
       </c>
       <c r="B7" t="n">
@@ -1015,7 +1003,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46141</v>
       </c>
       <c r="B8" t="n">
@@ -1023,7 +1011,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B9" t="n">
@@ -1031,7 +1019,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B10" t="n">
@@ -1039,7 +1027,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46144</v>
       </c>
       <c r="B11" t="n">
@@ -1047,7 +1035,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46145</v>
       </c>
       <c r="B12" t="n">
@@ -1055,7 +1043,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>46146</v>
       </c>
       <c r="B13" t="n">
@@ -1063,7 +1051,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="B14" t="n">
@@ -1071,7 +1059,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="B15" t="n">
@@ -1079,7 +1067,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="B16" t="n">
@@ -1087,7 +1075,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B17" t="n">
@@ -1095,7 +1083,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>46151</v>
       </c>
       <c r="B18" t="n">
@@ -1103,7 +1091,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>46152</v>
       </c>
       <c r="B19" t="n">
@@ -1111,7 +1099,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="B20" t="n">
@@ -1119,7 +1107,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="B21" t="n">
@@ -1127,7 +1115,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="B22" t="n">
@@ -1135,7 +1123,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46156</v>
       </c>
       <c r="B23" t="n">
@@ -1143,7 +1131,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B24" t="n">
@@ -1151,7 +1139,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46158</v>
       </c>
       <c r="B25" t="n">
@@ -1159,7 +1147,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46159</v>
       </c>
       <c r="B26" t="n">
@@ -1167,7 +1155,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="B27" t="n">
@@ -1175,7 +1163,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="B28" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="B29" t="n">
@@ -1191,7 +1179,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="B30" t="n">
@@ -1199,7 +1187,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B31" t="n">
@@ -1221,157 +1209,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>shipment_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>material_category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>material_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>quantity_mt</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>rate_per_mt</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sale_value_without_gst</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gst_rate_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gst_amount</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>invoice_amount</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>shipment_date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>delivered_date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>invoice_date</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>due_date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>vehicle_number</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>sales_order_id</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>amount_paid_total</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>outstanding</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>is_settled</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>due_date_parsed</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>days_to_due</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>days_overdue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>eligible_for_reminder</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>eligible_for_overdue</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>in_7d_window</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>in_3d_window</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>in_1d_window</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>aging_bucket</t>
         </is>
@@ -1465,7 +1453,7 @@
       <c r="S2" t="b">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="U2" t="n">
@@ -1598,7 +1586,7 @@
       <c r="S3" t="b">
         <v>0</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="T3" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="U3" t="n">
@@ -1731,7 +1719,7 @@
       <c r="S4" t="b">
         <v>0</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" s="1" t="n">
         <v>46116</v>
       </c>
       <c r="U4" t="n">
@@ -1864,7 +1852,7 @@
       <c r="S5" t="b">
         <v>0</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="U5" t="n">
@@ -1997,7 +1985,7 @@
       <c r="S6" t="b">
         <v>0</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" s="1" t="n">
         <v>46124</v>
       </c>
       <c r="U6" t="n">
@@ -2130,7 +2118,7 @@
       <c r="S7" t="b">
         <v>0</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" s="1" t="n">
         <v>46137</v>
       </c>
       <c r="U7" t="n">
@@ -2263,7 +2251,7 @@
       <c r="S8" t="b">
         <v>0</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="U8" t="n">
@@ -2396,7 +2384,7 @@
       <c r="S9" t="b">
         <v>0</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="T9" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="U9" t="n">
@@ -2529,7 +2517,7 @@
       <c r="S10" t="b">
         <v>0</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="T10" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="U10" t="n">
@@ -2662,7 +2650,7 @@
       <c r="S11" t="b">
         <v>0</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="T11" s="1" t="n">
         <v>46172</v>
       </c>
       <c r="U11" t="n">
@@ -2795,7 +2783,7 @@
       <c r="S12" t="b">
         <v>0</v>
       </c>
-      <c r="T12" s="2" t="n">
+      <c r="T12" s="1" t="n">
         <v>46160</v>
       </c>
       <c r="U12" t="n">
@@ -2928,7 +2916,7 @@
       <c r="S13" t="b">
         <v>0</v>
       </c>
-      <c r="T13" s="2" t="n">
+      <c r="T13" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="U13" t="n">
@@ -3061,7 +3049,7 @@
       <c r="S14" t="b">
         <v>0</v>
       </c>
-      <c r="T14" s="2" t="n">
+      <c r="T14" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U14" t="n">
@@ -3194,7 +3182,7 @@
       <c r="S15" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="T15" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U15" t="n">
@@ -3327,7 +3315,7 @@
       <c r="S16" t="b">
         <v>0</v>
       </c>
-      <c r="T16" s="2" t="n">
+      <c r="T16" s="1" t="n">
         <v>46186</v>
       </c>
       <c r="U16" t="n">
@@ -3460,7 +3448,7 @@
       <c r="S17" t="b">
         <v>0</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="T17" s="1" t="n">
         <v>46187</v>
       </c>
       <c r="U17" t="n">
@@ -3593,7 +3581,7 @@
       <c r="S18" t="b">
         <v>0</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="T18" s="1" t="n">
         <v>46189</v>
       </c>
       <c r="U18" t="n">
@@ -3726,7 +3714,7 @@
       <c r="S19" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="T19" s="1" t="n">
         <v>46189</v>
       </c>
       <c r="U19" t="n">
@@ -3859,7 +3847,7 @@
       <c r="S20" t="b">
         <v>0</v>
       </c>
-      <c r="T20" s="2" t="n">
+      <c r="T20" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U20" t="n">
@@ -3992,7 +3980,7 @@
       <c r="S21" t="b">
         <v>0</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="T21" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U21" t="n">
@@ -4125,7 +4113,7 @@
       <c r="S22" t="b">
         <v>0</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="T22" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U22" t="n">
@@ -4258,7 +4246,7 @@
       <c r="S23" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="2" t="n">
+      <c r="T23" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="U23" t="n">
@@ -4391,7 +4379,7 @@
       <c r="S24" t="b">
         <v>0</v>
       </c>
-      <c r="T24" s="2" t="n">
+      <c r="T24" s="1" t="n">
         <v>46194</v>
       </c>
       <c r="U24" t="n">
@@ -4524,7 +4512,7 @@
       <c r="S25" t="b">
         <v>0</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="T25" s="1" t="n">
         <v>46195</v>
       </c>
       <c r="U25" t="n">
@@ -4657,7 +4645,7 @@
       <c r="S26" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="2" t="n">
+      <c r="T26" s="1" t="n">
         <v>46180</v>
       </c>
       <c r="U26" t="n">
@@ -4790,7 +4778,7 @@
       <c r="S27" t="b">
         <v>0</v>
       </c>
-      <c r="T27" s="2" t="n">
+      <c r="T27" s="1" t="n">
         <v>46196</v>
       </c>
       <c r="U27" t="n">
@@ -4923,7 +4911,7 @@
       <c r="S28" t="b">
         <v>0</v>
       </c>
-      <c r="T28" s="2" t="n">
+      <c r="T28" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="U28" t="n">
@@ -5056,7 +5044,7 @@
       <c r="S29" t="b">
         <v>0</v>
       </c>
-      <c r="T29" s="2" t="n">
+      <c r="T29" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="U29" t="n">
@@ -5189,7 +5177,7 @@
       <c r="S30" t="b">
         <v>0</v>
       </c>
-      <c r="T30" s="2" t="n">
+      <c r="T30" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="U30" t="n">
@@ -5322,7 +5310,7 @@
       <c r="S31" t="b">
         <v>0</v>
       </c>
-      <c r="T31" s="2" t="n">
+      <c r="T31" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="U31" t="n">
@@ -5455,7 +5443,7 @@
       <c r="S32" t="b">
         <v>0</v>
       </c>
-      <c r="T32" s="2" t="n">
+      <c r="T32" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U32" t="n">
@@ -5588,7 +5576,7 @@
       <c r="S33" t="b">
         <v>0</v>
       </c>
-      <c r="T33" s="2" t="n">
+      <c r="T33" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U33" t="n">
@@ -5721,7 +5709,7 @@
       <c r="S34" t="b">
         <v>0</v>
       </c>
-      <c r="T34" s="2" t="n">
+      <c r="T34" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U34" t="n">
@@ -5854,7 +5842,7 @@
       <c r="S35" t="b">
         <v>0</v>
       </c>
-      <c r="T35" s="2" t="n">
+      <c r="T35" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U35" t="n">
@@ -5987,7 +5975,7 @@
       <c r="S36" t="b">
         <v>0</v>
       </c>
-      <c r="T36" s="2" t="n">
+      <c r="T36" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U36" t="n">
@@ -6120,7 +6108,7 @@
       <c r="S37" t="b">
         <v>0</v>
       </c>
-      <c r="T37" s="2" t="n">
+      <c r="T37" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U37" t="n">
@@ -6253,7 +6241,7 @@
       <c r="S38" t="b">
         <v>0</v>
       </c>
-      <c r="T38" s="2" t="n">
+      <c r="T38" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U38" t="n">
@@ -6386,7 +6374,7 @@
       <c r="S39" t="b">
         <v>0</v>
       </c>
-      <c r="T39" s="2" t="n">
+      <c r="T39" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U39" t="n">
@@ -6519,7 +6507,7 @@
       <c r="S40" t="b">
         <v>0</v>
       </c>
-      <c r="T40" s="2" t="n">
+      <c r="T40" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U40" t="n">
@@ -6652,7 +6640,7 @@
       <c r="S41" t="b">
         <v>0</v>
       </c>
-      <c r="T41" s="2" t="n">
+      <c r="T41" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U41" t="n">
@@ -6785,7 +6773,7 @@
       <c r="S42" t="b">
         <v>0</v>
       </c>
-      <c r="T42" s="2" t="n">
+      <c r="T42" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U42" t="n">
@@ -6918,7 +6906,7 @@
       <c r="S43" t="b">
         <v>0</v>
       </c>
-      <c r="T43" s="2" t="n">
+      <c r="T43" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U43" t="n">
@@ -7051,7 +7039,7 @@
       <c r="S44" t="b">
         <v>0</v>
       </c>
-      <c r="T44" s="2" t="n">
+      <c r="T44" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U44" t="n">
@@ -7184,7 +7172,7 @@
       <c r="S45" t="b">
         <v>0</v>
       </c>
-      <c r="T45" s="2" t="n">
+      <c r="T45" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U45" t="n">
@@ -7317,7 +7305,7 @@
       <c r="S46" t="b">
         <v>0</v>
       </c>
-      <c r="T46" s="2" t="n">
+      <c r="T46" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U46" t="n">
@@ -7450,7 +7438,7 @@
       <c r="S47" t="b">
         <v>0</v>
       </c>
-      <c r="T47" s="2" t="n">
+      <c r="T47" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U47" t="n">
@@ -7583,7 +7571,7 @@
       <c r="S48" t="b">
         <v>0</v>
       </c>
-      <c r="T48" s="2" t="n">
+      <c r="T48" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U48" t="n">
@@ -7716,7 +7704,7 @@
       <c r="S49" t="b">
         <v>0</v>
       </c>
-      <c r="T49" s="2" t="n">
+      <c r="T49" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U49" t="n">
@@ -7849,7 +7837,7 @@
       <c r="S50" t="b">
         <v>0</v>
       </c>
-      <c r="T50" s="2" t="n">
+      <c r="T50" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U50" t="n">
@@ -7982,7 +7970,7 @@
       <c r="S51" t="b">
         <v>0</v>
       </c>
-      <c r="T51" s="2" t="n">
+      <c r="T51" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U51" t="n">
@@ -8115,7 +8103,7 @@
       <c r="S52" t="b">
         <v>0</v>
       </c>
-      <c r="T52" s="2" t="n">
+      <c r="T52" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U52" t="n">
@@ -8248,7 +8236,7 @@
       <c r="S53" t="b">
         <v>0</v>
       </c>
-      <c r="T53" s="2" t="n">
+      <c r="T53" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U53" t="n">
@@ -8381,7 +8369,7 @@
       <c r="S54" t="b">
         <v>0</v>
       </c>
-      <c r="T54" s="2" t="n">
+      <c r="T54" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U54" t="n">
@@ -8514,7 +8502,7 @@
       <c r="S55" t="b">
         <v>0</v>
       </c>
-      <c r="T55" s="2" t="n">
+      <c r="T55" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U55" t="n">
@@ -8647,7 +8635,7 @@
       <c r="S56" t="b">
         <v>0</v>
       </c>
-      <c r="T56" s="2" t="n">
+      <c r="T56" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U56" t="n">
@@ -8780,7 +8768,7 @@
       <c r="S57" t="b">
         <v>0</v>
       </c>
-      <c r="T57" s="2" t="n">
+      <c r="T57" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U57" t="n">
@@ -8913,7 +8901,7 @@
       <c r="S58" t="b">
         <v>0</v>
       </c>
-      <c r="T58" s="2" t="n">
+      <c r="T58" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U58" t="n">
@@ -9046,7 +9034,7 @@
       <c r="S59" t="b">
         <v>0</v>
       </c>
-      <c r="T59" s="2" t="n">
+      <c r="T59" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U59" t="n">
@@ -9179,7 +9167,7 @@
       <c r="S60" t="b">
         <v>0</v>
       </c>
-      <c r="T60" s="2" t="n">
+      <c r="T60" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U60" t="n">
@@ -9312,7 +9300,7 @@
       <c r="S61" t="b">
         <v>0</v>
       </c>
-      <c r="T61" s="2" t="n">
+      <c r="T61" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U61" t="n">
@@ -9445,7 +9433,7 @@
       <c r="S62" t="b">
         <v>0</v>
       </c>
-      <c r="T62" s="2" t="n">
+      <c r="T62" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U62" t="n">
@@ -9578,7 +9566,7 @@
       <c r="S63" t="b">
         <v>0</v>
       </c>
-      <c r="T63" s="2" t="n">
+      <c r="T63" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U63" t="n">
@@ -9711,7 +9699,7 @@
       <c r="S64" t="b">
         <v>0</v>
       </c>
-      <c r="T64" s="2" t="n">
+      <c r="T64" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U64" t="n">
@@ -9844,7 +9832,7 @@
       <c r="S65" t="b">
         <v>0</v>
       </c>
-      <c r="T65" s="2" t="n">
+      <c r="T65" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U65" t="n">
@@ -9977,7 +9965,7 @@
       <c r="S66" t="b">
         <v>0</v>
       </c>
-      <c r="T66" s="2" t="n">
+      <c r="T66" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U66" t="n">
@@ -10110,7 +10098,7 @@
       <c r="S67" t="b">
         <v>0</v>
       </c>
-      <c r="T67" s="2" t="n">
+      <c r="T67" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U67" t="n">
@@ -10243,7 +10231,7 @@
       <c r="S68" t="b">
         <v>0</v>
       </c>
-      <c r="T68" s="2" t="n">
+      <c r="T68" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U68" t="n">
@@ -10376,7 +10364,7 @@
       <c r="S69" t="b">
         <v>0</v>
       </c>
-      <c r="T69" s="2" t="n">
+      <c r="T69" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U69" t="n">
@@ -10509,7 +10497,7 @@
       <c r="S70" t="b">
         <v>0</v>
       </c>
-      <c r="T70" s="2" t="n">
+      <c r="T70" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U70" t="n">
@@ -10642,7 +10630,7 @@
       <c r="S71" t="b">
         <v>0</v>
       </c>
-      <c r="T71" s="2" t="n">
+      <c r="T71" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U71" t="n">
@@ -10775,7 +10763,7 @@
       <c r="S72" t="b">
         <v>0</v>
       </c>
-      <c r="T72" s="2" t="n">
+      <c r="T72" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U72" t="n">
@@ -10908,7 +10896,7 @@
       <c r="S73" t="b">
         <v>0</v>
       </c>
-      <c r="T73" s="2" t="n">
+      <c r="T73" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U73" t="n">
@@ -11041,7 +11029,7 @@
       <c r="S74" t="b">
         <v>0</v>
       </c>
-      <c r="T74" s="2" t="n">
+      <c r="T74" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U74" t="n">
@@ -11174,7 +11162,7 @@
       <c r="S75" t="b">
         <v>0</v>
       </c>
-      <c r="T75" s="2" t="n">
+      <c r="T75" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U75" t="n">
@@ -11307,7 +11295,7 @@
       <c r="S76" t="b">
         <v>0</v>
       </c>
-      <c r="T76" s="2" t="n">
+      <c r="T76" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U76" t="n">
@@ -11440,7 +11428,7 @@
       <c r="S77" t="b">
         <v>0</v>
       </c>
-      <c r="T77" s="2" t="n">
+      <c r="T77" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U77" t="n">
@@ -11573,7 +11561,7 @@
       <c r="S78" t="b">
         <v>0</v>
       </c>
-      <c r="T78" s="2" t="n">
+      <c r="T78" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U78" t="n">
@@ -11706,7 +11694,7 @@
       <c r="S79" t="b">
         <v>0</v>
       </c>
-      <c r="T79" s="2" t="n">
+      <c r="T79" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U79" t="n">
@@ -11839,7 +11827,7 @@
       <c r="S80" t="b">
         <v>0</v>
       </c>
-      <c r="T80" s="2" t="n">
+      <c r="T80" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U80" t="n">
@@ -11972,7 +11960,7 @@
       <c r="S81" t="b">
         <v>0</v>
       </c>
-      <c r="T81" s="2" t="n">
+      <c r="T81" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U81" t="n">
@@ -12105,7 +12093,7 @@
       <c r="S82" t="b">
         <v>0</v>
       </c>
-      <c r="T82" s="2" t="n">
+      <c r="T82" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U82" t="n">
@@ -12238,7 +12226,7 @@
       <c r="S83" t="b">
         <v>0</v>
       </c>
-      <c r="T83" s="2" t="n">
+      <c r="T83" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U83" t="n">
@@ -12371,7 +12359,7 @@
       <c r="S84" t="b">
         <v>0</v>
       </c>
-      <c r="T84" s="2" t="n">
+      <c r="T84" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="U84" t="n">
@@ -12504,7 +12492,7 @@
       <c r="S85" t="b">
         <v>0</v>
       </c>
-      <c r="T85" s="2" t="n">
+      <c r="T85" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="U85" t="n">
@@ -12637,7 +12625,7 @@
       <c r="S86" t="b">
         <v>0</v>
       </c>
-      <c r="T86" s="2" t="n">
+      <c r="T86" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U86" t="n">
@@ -12770,7 +12758,7 @@
       <c r="S87" t="b">
         <v>0</v>
       </c>
-      <c r="T87" s="2" t="n">
+      <c r="T87" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U87" t="n">
@@ -12903,7 +12891,7 @@
       <c r="S88" t="b">
         <v>0</v>
       </c>
-      <c r="T88" s="2" t="n">
+      <c r="T88" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U88" t="n">
@@ -13036,7 +13024,7 @@
       <c r="S89" t="b">
         <v>0</v>
       </c>
-      <c r="T89" s="2" t="n">
+      <c r="T89" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U89" t="n">
@@ -13169,7 +13157,7 @@
       <c r="S90" t="b">
         <v>0</v>
       </c>
-      <c r="T90" s="2" t="n">
+      <c r="T90" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U90" t="n">
@@ -13302,7 +13290,7 @@
       <c r="S91" t="b">
         <v>0</v>
       </c>
-      <c r="T91" s="2" t="n">
+      <c r="T91" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U91" t="n">
@@ -13435,7 +13423,7 @@
       <c r="S92" t="b">
         <v>0</v>
       </c>
-      <c r="T92" s="2" t="n">
+      <c r="T92" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U92" t="n">
@@ -13568,7 +13556,7 @@
       <c r="S93" t="b">
         <v>0</v>
       </c>
-      <c r="T93" s="2" t="n">
+      <c r="T93" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U93" t="n">
@@ -13701,7 +13689,7 @@
       <c r="S94" t="b">
         <v>0</v>
       </c>
-      <c r="T94" s="2" t="n">
+      <c r="T94" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U94" t="n">
@@ -13834,7 +13822,7 @@
       <c r="S95" t="b">
         <v>0</v>
       </c>
-      <c r="T95" s="2" t="n">
+      <c r="T95" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U95" t="n">
@@ -13967,7 +13955,7 @@
       <c r="S96" t="b">
         <v>0</v>
       </c>
-      <c r="T96" s="2" t="n">
+      <c r="T96" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U96" t="n">
@@ -14100,7 +14088,7 @@
       <c r="S97" t="b">
         <v>0</v>
       </c>
-      <c r="T97" s="2" t="n">
+      <c r="T97" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U97" t="n">
@@ -14233,7 +14221,7 @@
       <c r="S98" t="b">
         <v>0</v>
       </c>
-      <c r="T98" s="2" t="n">
+      <c r="T98" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U98" t="n">
@@ -14366,7 +14354,7 @@
       <c r="S99" t="b">
         <v>0</v>
       </c>
-      <c r="T99" s="2" t="n">
+      <c r="T99" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U99" t="n">
@@ -14499,7 +14487,7 @@
       <c r="S100" t="b">
         <v>0</v>
       </c>
-      <c r="T100" s="2" t="n">
+      <c r="T100" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U100" t="n">
@@ -14632,7 +14620,7 @@
       <c r="S101" t="b">
         <v>0</v>
       </c>
-      <c r="T101" s="2" t="n">
+      <c r="T101" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U101" t="n">
@@ -14765,7 +14753,7 @@
       <c r="S102" t="b">
         <v>0</v>
       </c>
-      <c r="T102" s="2" t="n">
+      <c r="T102" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U102" t="n">
@@ -14898,7 +14886,7 @@
       <c r="S103" t="b">
         <v>0</v>
       </c>
-      <c r="T103" s="2" t="n">
+      <c r="T103" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U103" t="n">
@@ -15031,7 +15019,7 @@
       <c r="S104" t="b">
         <v>0</v>
       </c>
-      <c r="T104" s="2" t="n">
+      <c r="T104" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U104" t="n">
@@ -15164,7 +15152,7 @@
       <c r="S105" t="b">
         <v>0</v>
       </c>
-      <c r="T105" s="2" t="n">
+      <c r="T105" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U105" t="n">
@@ -15297,7 +15285,7 @@
       <c r="S106" t="b">
         <v>0</v>
       </c>
-      <c r="T106" s="2" t="n">
+      <c r="T106" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U106" t="n">
@@ -15430,7 +15418,7 @@
       <c r="S107" t="b">
         <v>0</v>
       </c>
-      <c r="T107" s="2" t="n">
+      <c r="T107" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U107" t="n">
@@ -15563,7 +15551,7 @@
       <c r="S108" t="b">
         <v>0</v>
       </c>
-      <c r="T108" s="2" t="n">
+      <c r="T108" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U108" t="n">
@@ -15696,7 +15684,7 @@
       <c r="S109" t="b">
         <v>0</v>
       </c>
-      <c r="T109" s="2" t="n">
+      <c r="T109" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U109" t="n">
@@ -15829,7 +15817,7 @@
       <c r="S110" t="b">
         <v>0</v>
       </c>
-      <c r="T110" s="2" t="n">
+      <c r="T110" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U110" t="n">
@@ -15962,7 +15950,7 @@
       <c r="S111" t="b">
         <v>0</v>
       </c>
-      <c r="T111" s="2" t="n">
+      <c r="T111" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U111" t="n">
@@ -16095,7 +16083,7 @@
       <c r="S112" t="b">
         <v>0</v>
       </c>
-      <c r="T112" s="2" t="n">
+      <c r="T112" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U112" t="n">
@@ -16228,7 +16216,7 @@
       <c r="S113" t="b">
         <v>0</v>
       </c>
-      <c r="T113" s="2" t="n">
+      <c r="T113" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U113" t="n">
@@ -16361,7 +16349,7 @@
       <c r="S114" t="b">
         <v>0</v>
       </c>
-      <c r="T114" s="2" t="n">
+      <c r="T114" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U114" t="n">
@@ -16494,7 +16482,7 @@
       <c r="S115" t="b">
         <v>0</v>
       </c>
-      <c r="T115" s="2" t="n">
+      <c r="T115" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U115" t="n">
@@ -16627,7 +16615,7 @@
       <c r="S116" t="b">
         <v>0</v>
       </c>
-      <c r="T116" s="2" t="n">
+      <c r="T116" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U116" t="n">
@@ -16760,7 +16748,7 @@
       <c r="S117" t="b">
         <v>0</v>
       </c>
-      <c r="T117" s="2" t="n">
+      <c r="T117" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U117" t="n">
@@ -16893,7 +16881,7 @@
       <c r="S118" t="b">
         <v>0</v>
       </c>
-      <c r="T118" s="2" t="n">
+      <c r="T118" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U118" t="n">
@@ -17026,7 +17014,7 @@
       <c r="S119" t="b">
         <v>0</v>
       </c>
-      <c r="T119" s="2" t="n">
+      <c r="T119" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U119" t="n">
@@ -17159,7 +17147,7 @@
       <c r="S120" t="b">
         <v>0</v>
       </c>
-      <c r="T120" s="2" t="n">
+      <c r="T120" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U120" t="n">
@@ -17292,7 +17280,7 @@
       <c r="S121" t="b">
         <v>0</v>
       </c>
-      <c r="T121" s="2" t="n">
+      <c r="T121" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U121" t="n">
@@ -17425,7 +17413,7 @@
       <c r="S122" t="b">
         <v>0</v>
       </c>
-      <c r="T122" s="2" t="n">
+      <c r="T122" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U122" t="n">
@@ -17558,7 +17546,7 @@
       <c r="S123" t="b">
         <v>0</v>
       </c>
-      <c r="T123" s="2" t="n">
+      <c r="T123" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U123" t="n">
@@ -17691,7 +17679,7 @@
       <c r="S124" t="b">
         <v>0</v>
       </c>
-      <c r="T124" s="2" t="n">
+      <c r="T124" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U124" t="n">
@@ -17824,7 +17812,7 @@
       <c r="S125" t="b">
         <v>0</v>
       </c>
-      <c r="T125" s="2" t="n">
+      <c r="T125" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U125" t="n">
@@ -17957,7 +17945,7 @@
       <c r="S126" t="b">
         <v>0</v>
       </c>
-      <c r="T126" s="2" t="n">
+      <c r="T126" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U126" t="n">
@@ -18090,7 +18078,7 @@
       <c r="S127" t="b">
         <v>0</v>
       </c>
-      <c r="T127" s="2" t="n">
+      <c r="T127" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U127" t="n">
@@ -18223,7 +18211,7 @@
       <c r="S128" t="b">
         <v>0</v>
       </c>
-      <c r="T128" s="2" t="n">
+      <c r="T128" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U128" t="n">
@@ -18356,7 +18344,7 @@
       <c r="S129" t="b">
         <v>0</v>
       </c>
-      <c r="T129" s="2" t="n">
+      <c r="T129" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U129" t="n">
@@ -18489,7 +18477,7 @@
       <c r="S130" t="b">
         <v>0</v>
       </c>
-      <c r="T130" s="2" t="n">
+      <c r="T130" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U130" t="n">
@@ -18622,7 +18610,7 @@
       <c r="S131" t="b">
         <v>0</v>
       </c>
-      <c r="T131" s="2" t="n">
+      <c r="T131" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U131" t="n">
@@ -18755,7 +18743,7 @@
       <c r="S132" t="b">
         <v>0</v>
       </c>
-      <c r="T132" s="2" t="n">
+      <c r="T132" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U132" t="n">
@@ -18888,7 +18876,7 @@
       <c r="S133" t="b">
         <v>0</v>
       </c>
-      <c r="T133" s="2" t="n">
+      <c r="T133" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U133" t="n">
@@ -19021,7 +19009,7 @@
       <c r="S134" t="b">
         <v>0</v>
       </c>
-      <c r="T134" s="2" t="n">
+      <c r="T134" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U134" t="n">
@@ -19154,7 +19142,7 @@
       <c r="S135" t="b">
         <v>0</v>
       </c>
-      <c r="T135" s="2" t="n">
+      <c r="T135" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U135" t="n">
@@ -19287,7 +19275,7 @@
       <c r="S136" t="b">
         <v>0</v>
       </c>
-      <c r="T136" s="2" t="n">
+      <c r="T136" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U136" t="n">
@@ -19420,7 +19408,7 @@
       <c r="S137" t="b">
         <v>0</v>
       </c>
-      <c r="T137" s="2" t="n">
+      <c r="T137" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U137" t="n">
@@ -19553,7 +19541,7 @@
       <c r="S138" t="b">
         <v>0</v>
       </c>
-      <c r="T138" s="2" t="n">
+      <c r="T138" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U138" t="n">
@@ -19686,7 +19674,7 @@
       <c r="S139" t="b">
         <v>0</v>
       </c>
-      <c r="T139" s="2" t="n">
+      <c r="T139" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U139" t="n">
@@ -19819,7 +19807,7 @@
       <c r="S140" t="b">
         <v>0</v>
       </c>
-      <c r="T140" s="2" t="n">
+      <c r="T140" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U140" t="n">
@@ -19952,7 +19940,7 @@
       <c r="S141" t="b">
         <v>0</v>
       </c>
-      <c r="T141" s="2" t="n">
+      <c r="T141" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U141" t="n">
@@ -20085,7 +20073,7 @@
       <c r="S142" t="b">
         <v>0</v>
       </c>
-      <c r="T142" s="2" t="n">
+      <c r="T142" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U142" t="n">
@@ -20218,7 +20206,7 @@
       <c r="S143" t="b">
         <v>0</v>
       </c>
-      <c r="T143" s="2" t="n">
+      <c r="T143" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U143" t="n">
@@ -20351,7 +20339,7 @@
       <c r="S144" t="b">
         <v>0</v>
       </c>
-      <c r="T144" s="2" t="n">
+      <c r="T144" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U144" t="n">
@@ -20484,7 +20472,7 @@
       <c r="S145" t="b">
         <v>0</v>
       </c>
-      <c r="T145" s="2" t="n">
+      <c r="T145" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U145" t="n">
@@ -20617,7 +20605,7 @@
       <c r="S146" t="b">
         <v>0</v>
       </c>
-      <c r="T146" s="2" t="n">
+      <c r="T146" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U146" t="n">
@@ -20750,7 +20738,7 @@
       <c r="S147" t="b">
         <v>0</v>
       </c>
-      <c r="T147" s="2" t="n">
+      <c r="T147" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U147" t="n">
@@ -20883,7 +20871,7 @@
       <c r="S148" t="b">
         <v>0</v>
       </c>
-      <c r="T148" s="2" t="n">
+      <c r="T148" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U148" t="n">
@@ -21016,7 +21004,7 @@
       <c r="S149" t="b">
         <v>0</v>
       </c>
-      <c r="T149" s="2" t="n">
+      <c r="T149" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U149" t="n">
@@ -21149,7 +21137,7 @@
       <c r="S150" t="b">
         <v>0</v>
       </c>
-      <c r="T150" s="2" t="n">
+      <c r="T150" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U150" t="n">
@@ -21282,7 +21270,7 @@
       <c r="S151" t="b">
         <v>0</v>
       </c>
-      <c r="T151" s="2" t="n">
+      <c r="T151" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U151" t="n">
@@ -21415,7 +21403,7 @@
       <c r="S152" t="b">
         <v>0</v>
       </c>
-      <c r="T152" s="2" t="n">
+      <c r="T152" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U152" t="n">
@@ -21548,7 +21536,7 @@
       <c r="S153" t="b">
         <v>0</v>
       </c>
-      <c r="T153" s="2" t="n">
+      <c r="T153" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U153" t="n">
@@ -21681,7 +21669,7 @@
       <c r="S154" t="b">
         <v>0</v>
       </c>
-      <c r="T154" s="2" t="n">
+      <c r="T154" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U154" t="n">
@@ -21814,7 +21802,7 @@
       <c r="S155" t="b">
         <v>0</v>
       </c>
-      <c r="T155" s="2" t="n">
+      <c r="T155" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U155" t="n">
@@ -21947,7 +21935,7 @@
       <c r="S156" t="b">
         <v>0</v>
       </c>
-      <c r="T156" s="2" t="n">
+      <c r="T156" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U156" t="n">
@@ -22080,7 +22068,7 @@
       <c r="S157" t="b">
         <v>0</v>
       </c>
-      <c r="T157" s="2" t="n">
+      <c r="T157" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U157" t="n">
@@ -22213,7 +22201,7 @@
       <c r="S158" t="b">
         <v>0</v>
       </c>
-      <c r="T158" s="2" t="n">
+      <c r="T158" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U158" t="n">
@@ -22346,7 +22334,7 @@
       <c r="S159" t="b">
         <v>0</v>
       </c>
-      <c r="T159" s="2" t="n">
+      <c r="T159" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U159" t="n">
@@ -22479,7 +22467,7 @@
       <c r="S160" t="b">
         <v>0</v>
       </c>
-      <c r="T160" s="2" t="n">
+      <c r="T160" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U160" t="n">
@@ -22612,7 +22600,7 @@
       <c r="S161" t="b">
         <v>0</v>
       </c>
-      <c r="T161" s="2" t="n">
+      <c r="T161" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="U161" t="n">
@@ -22745,7 +22733,7 @@
       <c r="S162" t="b">
         <v>0</v>
       </c>
-      <c r="T162" s="2" t="n">
+      <c r="T162" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="U162" t="n">
@@ -22878,7 +22866,7 @@
       <c r="S163" t="b">
         <v>0</v>
       </c>
-      <c r="T163" s="2" t="n">
+      <c r="T163" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U163" t="n">
@@ -23011,7 +22999,7 @@
       <c r="S164" t="b">
         <v>0</v>
       </c>
-      <c r="T164" s="2" t="n">
+      <c r="T164" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U164" t="n">
@@ -23144,7 +23132,7 @@
       <c r="S165" t="b">
         <v>0</v>
       </c>
-      <c r="T165" s="2" t="n">
+      <c r="T165" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U165" t="n">
@@ -23277,7 +23265,7 @@
       <c r="S166" t="b">
         <v>0</v>
       </c>
-      <c r="T166" s="2" t="n">
+      <c r="T166" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U166" t="n">
@@ -23410,7 +23398,7 @@
       <c r="S167" t="b">
         <v>0</v>
       </c>
-      <c r="T167" s="2" t="n">
+      <c r="T167" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U167" t="n">
@@ -23543,7 +23531,7 @@
       <c r="S168" t="b">
         <v>0</v>
       </c>
-      <c r="T168" s="2" t="n">
+      <c r="T168" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U168" t="n">
@@ -23676,7 +23664,7 @@
       <c r="S169" t="b">
         <v>0</v>
       </c>
-      <c r="T169" s="2" t="n">
+      <c r="T169" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U169" t="n">
@@ -23809,7 +23797,7 @@
       <c r="S170" t="b">
         <v>0</v>
       </c>
-      <c r="T170" s="2" t="n">
+      <c r="T170" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U170" t="n">
@@ -23942,7 +23930,7 @@
       <c r="S171" t="b">
         <v>0</v>
       </c>
-      <c r="T171" s="2" t="n">
+      <c r="T171" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U171" t="n">
@@ -24075,7 +24063,7 @@
       <c r="S172" t="b">
         <v>0</v>
       </c>
-      <c r="T172" s="2" t="n">
+      <c r="T172" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U172" t="n">
@@ -24208,7 +24196,7 @@
       <c r="S173" t="b">
         <v>0</v>
       </c>
-      <c r="T173" s="2" t="n">
+      <c r="T173" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U173" t="n">
@@ -24341,7 +24329,7 @@
       <c r="S174" t="b">
         <v>0</v>
       </c>
-      <c r="T174" s="2" t="n">
+      <c r="T174" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U174" t="n">
@@ -24474,7 +24462,7 @@
       <c r="S175" t="b">
         <v>0</v>
       </c>
-      <c r="T175" s="2" t="n">
+      <c r="T175" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="U175" t="n">
@@ -24607,7 +24595,7 @@
       <c r="S176" t="b">
         <v>0</v>
       </c>
-      <c r="T176" s="2" t="n">
+      <c r="T176" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U176" t="n">
@@ -24740,7 +24728,7 @@
       <c r="S177" t="b">
         <v>0</v>
       </c>
-      <c r="T177" s="2" t="n">
+      <c r="T177" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U177" t="n">
@@ -24873,7 +24861,7 @@
       <c r="S178" t="b">
         <v>0</v>
       </c>
-      <c r="T178" s="2" t="n">
+      <c r="T178" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="U178" t="n">
@@ -25006,7 +24994,7 @@
       <c r="S179" t="b">
         <v>0</v>
       </c>
-      <c r="T179" s="2" t="n">
+      <c r="T179" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U179" t="n">
@@ -25139,7 +25127,7 @@
       <c r="S180" t="b">
         <v>0</v>
       </c>
-      <c r="T180" s="2" t="n">
+      <c r="T180" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U180" t="n">
@@ -25272,7 +25260,7 @@
       <c r="S181" t="b">
         <v>0</v>
       </c>
-      <c r="T181" s="2" t="n">
+      <c r="T181" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U181" t="n">
@@ -25405,7 +25393,7 @@
       <c r="S182" t="b">
         <v>0</v>
       </c>
-      <c r="T182" s="2" t="n">
+      <c r="T182" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U182" t="n">
@@ -25538,7 +25526,7 @@
       <c r="S183" t="b">
         <v>0</v>
       </c>
-      <c r="T183" s="2" t="n">
+      <c r="T183" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U183" t="n">
@@ -25671,7 +25659,7 @@
       <c r="S184" t="b">
         <v>0</v>
       </c>
-      <c r="T184" s="2" t="n">
+      <c r="T184" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U184" t="n">
@@ -25804,7 +25792,7 @@
       <c r="S185" t="b">
         <v>0</v>
       </c>
-      <c r="T185" s="2" t="n">
+      <c r="T185" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U185" t="n">
@@ -25937,7 +25925,7 @@
       <c r="S186" t="b">
         <v>0</v>
       </c>
-      <c r="T186" s="2" t="n">
+      <c r="T186" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U186" t="n">
@@ -26070,7 +26058,7 @@
       <c r="S187" t="b">
         <v>0</v>
       </c>
-      <c r="T187" s="2" t="n">
+      <c r="T187" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U187" t="n">
@@ -26203,7 +26191,7 @@
       <c r="S188" t="b">
         <v>0</v>
       </c>
-      <c r="T188" s="2" t="n">
+      <c r="T188" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U188" t="n">
@@ -26336,7 +26324,7 @@
       <c r="S189" t="b">
         <v>0</v>
       </c>
-      <c r="T189" s="2" t="n">
+      <c r="T189" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="U189" t="n">
@@ -26469,7 +26457,7 @@
       <c r="S190" t="b">
         <v>0</v>
       </c>
-      <c r="T190" s="2" t="n">
+      <c r="T190" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U190" t="n">
@@ -26602,7 +26590,7 @@
       <c r="S191" t="b">
         <v>0</v>
       </c>
-      <c r="T191" s="2" t="n">
+      <c r="T191" s="1" t="n">
         <v>46193</v>
       </c>
       <c r="U191" t="n">

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -956,159 +956,159 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B2" t="n">
-        <v>10281291.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>11750336.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B4" t="n">
-        <v>11750336.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>18312295.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B6" t="n">
-        <v>18312295.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>4194477.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B8" t="n">
-        <v>4194477.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B10" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B12" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B13" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B14" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B15" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B16" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B18" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B20" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -1140,47 +1140,47 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B26" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B27" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B28" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B29" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="V2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-66</v>
+        <v>-67</v>
       </c>
       <c r="V3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="V4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="V5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="V6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="V7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="b">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="AB11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="b">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -956,151 +956,151 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>11750336.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B3" t="n">
-        <v>11750336.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>18312295.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B5" t="n">
-        <v>18312295.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>4194477.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B7" t="n">
-        <v>4194477.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B9" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B11" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B12" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B13" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B14" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B15" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B17" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B19" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -1132,47 +1132,47 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B25" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B26" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B27" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B28" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="V2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-67</v>
+        <v>-68</v>
       </c>
       <c r="V3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="V4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="V5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="V6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="V7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="b">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="AB11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="b">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -956,143 +956,143 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B2" t="n">
-        <v>11750336.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>18312295.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B4" t="n">
-        <v>18312295.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4194477.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B6" t="n">
-        <v>4194477.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B8" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B10" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B11" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B12" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B13" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B14" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B16" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B18" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
@@ -1124,47 +1124,47 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B24" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B25" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B26" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B27" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-71</v>
+        <v>-72</v>
       </c>
       <c r="V2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="V3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="V4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="V5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="V6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="V7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="V13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53575190.23</v>
+        <v>52789910.07</v>
       </c>
     </row>
     <row r="4">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7297067.82</v>
+        <v>8082347.98</v>
       </c>
     </row>
     <row r="5">
@@ -956,135 +956,135 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>18312295.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B3" t="n">
-        <v>18312295.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4194477.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B5" t="n">
-        <v>4194477.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B7" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B9" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B10" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B11" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B12" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B13" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B15" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B17" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
@@ -1116,47 +1116,47 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B23" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B24" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B25" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B26" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-72</v>
+        <v>-73</v>
       </c>
       <c r="V2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="V3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="V4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="V5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="V6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="V7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1-30 Days Overdue</t>
+          <t>31-60 Days Overdue</t>
         </is>
       </c>
     </row>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -956,127 +956,127 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B2" t="n">
-        <v>18312295.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4194477.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B4" t="n">
-        <v>4194477.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B6" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B8" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B9" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B10" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B11" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B12" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B14" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B16" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -1108,47 +1108,47 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B22" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B23" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B24" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B25" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-73</v>
+        <v>-74</v>
       </c>
       <c r="V2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="V3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="V4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="V5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="V6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="V7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="AC10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="AC11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>533200026.29</v>
+        <v>530409307.7</v>
       </c>
     </row>
     <row r="3">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52789910.07</v>
+        <v>55580628.66</v>
       </c>
     </row>
     <row r="4">
@@ -956,119 +956,119 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4194477.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B3" t="n">
-        <v>4194477.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B5" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B7" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B8" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B9" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B10" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B11" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B13" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B15" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -1100,47 +1100,47 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B21" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B22" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B23" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B24" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-74</v>
+        <v>-75</v>
       </c>
       <c r="V2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-71</v>
+        <v>-72</v>
       </c>
       <c r="V3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="V4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="V5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="V6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="V7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="AA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="b">
         <v>0</v>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Not Yet Due</t>
+          <t>1-30 Days Overdue</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="AC10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="AC11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -956,111 +956,111 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B2" t="n">
-        <v>4194477.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B4" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B6" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B7" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B8" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B9" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B10" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B12" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B14" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -1092,47 +1092,47 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B20" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B21" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B22" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B23" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-75</v>
+        <v>-76</v>
       </c>
       <c r="V2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-72</v>
+        <v>-73</v>
       </c>
       <c r="V3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="V4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="V5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="V6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="V7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="AB14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="b">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AB15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="b">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="AB23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="b">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -956,103 +956,103 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>35803141.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B3" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B5" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B6" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B7" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B8" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B9" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B11" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B13" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1084,47 +1084,47 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B19" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B20" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B21" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B22" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-76</v>
+        <v>-77</v>
       </c>
       <c r="V2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-73</v>
+        <v>-74</v>
       </c>
       <c r="V3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="V4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="V5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="V6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="V7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="AB14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="b">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AB15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="b">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="AB23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="b">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>

--- a/deploy/collections_dashboard.xlsx
+++ b/deploy/collections_dashboard.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>530409307.7</v>
+        <v>521141403.54</v>
       </c>
     </row>
     <row r="3">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55580628.66</v>
+        <v>64848532.82</v>
       </c>
     </row>
     <row r="4">
@@ -956,95 +956,95 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B2" t="n">
-        <v>35803141.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>25121142.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B4" t="n">
-        <v>25121142.79</v>
+        <v>5124637.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B5" t="n">
-        <v>5124637.23</v>
+        <v>15042741.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B6" t="n">
-        <v>15042741.71</v>
+        <v>11924590.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B7" t="n">
-        <v>11924590.24</v>
+        <v>17680311.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B8" t="n">
-        <v>17680311.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>62221157.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B10" t="n">
-        <v>62221157.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>33385933.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B12" t="n">
-        <v>33385933.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -1076,47 +1076,47 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>325262056.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B18" t="n">
-        <v>325262056.87</v>
+        <v>410540223.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B19" t="n">
-        <v>410540223.49</v>
+        <v>89536410.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B20" t="n">
-        <v>89536410.31</v>
+        <v>74694779.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B21" t="n">
-        <v>74694779.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>46095</v>
       </c>
       <c r="U2" t="n">
-        <v>-77</v>
+        <v>-78</v>
       </c>
       <c r="V2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>46098</v>
       </c>
       <c r="U3" t="n">
-        <v>-74</v>
+        <v>-75</v>
       </c>
       <c r="V3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>46116</v>
       </c>
       <c r="U4" t="n">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="V4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         <v>46122</v>
       </c>
       <c r="U5" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="V5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>46124</v>
       </c>
       <c r="U6" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="V6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         <v>46137</v>
       </c>
       <c r="U7" t="n">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="V7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>46160</v>
       </c>
       <c r="U8" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="V8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         <v>46169</v>
       </c>
       <c r="U9" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         <v>46172</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="b">
         <v>0</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Not Yet Due</t>
+          <t>1-30 Days Overdue</t>
         </is>
       </c>
     </row>
@@ -2654,10 +2654,10 @@
         <v>46172</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Not Yet Due</t>
+          <t>1-30 Days Overdue</t>
         </is>
       </c>
     </row>
@@ -2787,10 +2787,10 @@
         <v>46160</v>
       </c>
       <c r="U12" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>46163</v>
       </c>
       <c r="U13" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46178</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         <v>46178</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>46186</v>
       </c>
       <c r="U16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>46187</v>
       </c>
       <c r="U17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46189</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>46189</v>
       </c>
       <c r="U19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>46190</v>
       </c>
       <c r="U20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>46192</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>46192</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>46178</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4383,7 +4383,7 @@
         <v>46194</v>
       </c>
       <c r="U24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>46195</v>
       </c>
       <c r="U25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>46180</v>
       </c>
       <c r="U26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="AB26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="b">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>46196</v>
       </c>
       <c r="U27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46182</v>
       </c>
       <c r="U28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>46182</v>
       </c>
       <c r="U29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>46197</v>
       </c>
       <c r="U30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
         <v>46197</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>46190</v>
       </c>
       <c r="U32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>46205</v>
       </c>
       <c r="U33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>46190</v>
       </c>
       <c r="U34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>46205</v>
       </c>
       <c r="U35" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>46190</v>
       </c>
       <c r="U36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>46205</v>
       </c>
       <c r="U37" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>46205</v>
       </c>
       <c r="U38" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6378,7 +6378,7 @@
         <v>46205</v>
       </c>
       <c r="U39" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -6511,7 +6511,7 @@
         <v>46205</v>
       </c>
       <c r="U40" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
         <v>46205</v>
       </c>
       <c r="U41" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>46190</v>
       </c>
       <c r="U42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>46205</v>
       </c>
       <c r="U43" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>46190</v>
       </c>
       <c r="U44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
         <v>46190</v>
       </c>
       <c r="U45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>46190</v>
       </c>
       <c r="U46" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>46190</v>
       </c>
       <c r="U47" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>46205</v>
       </c>
       <c r="U48" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
         <v>46205</v>
       </c>
       <c r="U49" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>46190</v>
       </c>
       <c r="U50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>46190</v>
       </c>
       <c r="U51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         <v>46205</v>
       </c>
       <c r="U52" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>46190</v>
       </c>
       <c r="U53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>46190</v>
       </c>
       <c r="U54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
         <v>46190</v>
       </c>
       <c r="U55" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -8639,7 +8639,7 @@
         <v>46190</v>
       </c>
       <c r="U56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         <v>46205</v>
       </c>
       <c r="U57" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>46205</v>
       </c>
       <c r="U58" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
         <v>46205</v>
       </c>
       <c r="U59" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>46190</v>
       </c>
       <c r="U60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>46190</v>
       </c>
       <c r="U61" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>46205</v>
       </c>
       <c r="U62" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>46205</v>
       </c>
       <c r="U63" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         <v>46205</v>
       </c>
       <c r="U64" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         <v>46205</v>
       </c>
       <c r="U65" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>46205</v>
       </c>
       <c r="U66" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>46190</v>
       </c>
       <c r="U67" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>46190</v>
       </c>
       <c r="U68" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>46205</v>
       </c>
       <c r="U69" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         <v>46205</v>
       </c>
       <c r="U70" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -10634,7 +10634,7 @@
         <v>46190</v>
       </c>
       <c r="U71" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -10767,7 +10767,7 @@
         <v>46190</v>
       </c>
       <c r="U72" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>46205</v>
       </c>
       <c r="U73" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -11033,7 +11033,7 @@
         <v>46205</v>
       </c>
       <c r="U74" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>46205</v>
       </c>
       <c r="U75" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>46205</v>
       </c>
       <c r="U76" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>46190</v>
       </c>
       <c r="U77" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>46205</v>
       </c>
       <c r="U78" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
         <v>46205</v>
       </c>
       <c r="U79" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -11831,7 +11831,7 @@
         <v>46205</v>
       </c>
       <c r="U80" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         <v>46190</v>
       </c>
       <c r="U81" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12097,7 +12097,7 @@
         <v>46190</v>
       </c>
       <c r="U82" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>46190</v>
       </c>
       <c r="U83" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>46190</v>
       </c>
       <c r="U84" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -12496,7 +12496,7 @@
         <v>46205</v>
       </c>
       <c r="U85" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>46191</v>
       </c>
       <c r="U86" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>46206</v>
       </c>
       <c r="U87" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         <v>46191</v>
       </c>
       <c r="U88" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
@@ -13028,7 +13028,7 @@
         <v>46191</v>
       </c>
       <c r="U89" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>46191</v>
       </c>
       <c r="U90" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -13294,7 +13294,7 @@
         <v>46191</v>
       </c>
       <c r="U91" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>46206</v>
       </c>
       <c r="U92" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V92" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46191</v>
       </c>
       <c r="U93" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -13693,7 +13693,7 @@
         <v>46206</v>
       </c>
       <c r="U94" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>46191</v>
       </c>
       <c r="U95" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -13959,7 +13959,7 @@
         <v>46206</v>
       </c>
       <c r="U96" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>46206</v>
       </c>
       <c r="U97" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
         <v>46191</v>
       </c>
       <c r="U98" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V98" t="n">
         <v>0</v>
@@ -14358,7 +14358,7 @@
         <v>46206</v>
       </c>
       <c r="U99" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -14491,7 +14491,7 @@
         <v>46206</v>
       </c>
       <c r="U100" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V100" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>46206</v>
       </c>
       <c r="U101" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>46191</v>
       </c>
       <c r="U102" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14890,7 +14890,7 @@
         <v>46206</v>
       </c>
       <c r="U103" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -15023,7 +15023,7 @@
         <v>46206</v>
       </c>
       <c r="U104" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>46206</v>
       </c>
       <c r="U105" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         <v>46191</v>
       </c>
       <c r="U106" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         <v>46206</v>
       </c>
       <c r="U107" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>46206</v>
       </c>
       <c r="U108" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -15688,7 +15688,7 @@
         <v>46206</v>
       </c>
       <c r="U109" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
         <v>46191</v>
       </c>
       <c r="U110" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>46206</v>
       </c>
       <c r="U111" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>46191</v>
       </c>
       <c r="U112" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16220,7 +16220,7 @@
         <v>46206</v>
       </c>
       <c r="U113" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -16353,7 +16353,7 @@
         <v>46206</v>
       </c>
       <c r="U114" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>46191</v>
       </c>
       <c r="U115" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
         <v>46191</v>
       </c>
       <c r="U116" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -16752,7 +16752,7 @@
         <v>46191</v>
       </c>
       <c r="U117" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         <v>46191</v>
       </c>
       <c r="U118" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>46191</v>
       </c>
       <c r="U119" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>46191</v>
       </c>
       <c r="U120" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>46206</v>
       </c>
       <c r="U121" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -17417,7 +17417,7 @@
         <v>46206</v>
       </c>
       <c r="U122" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17550,7 +17550,7 @@
         <v>46206</v>
       </c>
       <c r="U123" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         <v>46191</v>
       </c>
       <c r="U124" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V124" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>46191</v>
       </c>
       <c r="U125" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
         <v>46191</v>
       </c>
       <c r="U126" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
@@ -18082,7 +18082,7 @@
         <v>46206</v>
       </c>
       <c r="U127" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V127" t="n">
         <v>0</v>
@@ -18215,7 +18215,7 @@
         <v>46206</v>
       </c>
       <c r="U128" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V128" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>46191</v>
       </c>
       <c r="U129" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -18481,7 +18481,7 @@
         <v>46206</v>
       </c>
       <c r="U130" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V130" t="n">
         <v>0</v>
@@ -18614,7 +18614,7 @@
         <v>46191</v>
       </c>
       <c r="U131" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -18747,7 +18747,7 @@
         <v>46206</v>
       </c>
       <c r="U132" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>46191</v>
       </c>
       <c r="U133" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -19013,7 +19013,7 @@
         <v>46206</v>
       </c>
       <c r="U134" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -19146,7 +19146,7 @@
         <v>46191</v>
       </c>
       <c r="U135" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -19279,7 +19279,7 @@
         <v>46206</v>
       </c>
       <c r="U136" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>46206</v>
       </c>
       <c r="U137" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19545,7 +19545,7 @@
         <v>46206</v>
       </c>
       <c r="U138" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>46191</v>
       </c>
       <c r="U139" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
         <v>46206</v>
       </c>
       <c r="U140" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>46206</v>
       </c>
       <c r="U141" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>46191</v>
       </c>
       <c r="U142" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>46206</v>
       </c>
       <c r="U143" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -20343,7 +20343,7 @@
         <v>46206</v>
       </c>
       <c r="U144" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
         <v>46191</v>
       </c>
       <c r="U145" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -20609,7 +20609,7 @@
         <v>46191</v>
       </c>
       <c r="U146" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V146" t="n">
         <v>0</v>
@@ -20742,7 +20742,7 @@
         <v>46206</v>
       </c>
       <c r="U147" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>46191</v>
       </c>
       <c r="U148" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V148" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
         <v>46191</v>
       </c>
       <c r="U149" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V149" t="n">
         <v>0</v>
@@ -21141,7 +21141,7 @@
         <v>46206</v>
       </c>
       <c r="U150" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V150" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46206</v>
       </c>
       <c r="U151" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -21407,7 +21407,7 @@
         <v>46191</v>
       </c>
       <c r="U152" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V152" t="n">
         <v>0</v>
@@ -21540,7 +21540,7 @@
         <v>46191</v>
       </c>
       <c r="U153" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
         <v>46206</v>
       </c>
       <c r="U154" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V154" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>46191</v>
       </c>
       <c r="U155" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -21939,7 +21939,7 @@
         <v>46206</v>
       </c>
       <c r="U156" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -22072,7 +22072,7 @@
         <v>46206</v>
       </c>
       <c r="U157" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -22205,7 +22205,7 @@
         <v>46191</v>
       </c>
       <c r="U158" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -22338,7 +22338,7 @@
         <v>46206</v>
       </c>
       <c r="U159" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -22471,7 +22471,7 @@
         <v>46206</v>
       </c>
       <c r="U160" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         <v>46206</v>
       </c>
       <c r="U161" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -22737,7 +22737,7 @@
         <v>46191</v>
       </c>
       <c r="U162" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -22870,7 +22870,7 @@
         <v>46192</v>
       </c>
       <c r="U163" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>46207</v>
       </c>
       <c r="U164" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -23136,7 +23136,7 @@
         <v>46192</v>
       </c>
       <c r="U165" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -23269,7 +23269,7 @@
         <v>46207</v>
       </c>
       <c r="U166" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -23402,7 +23402,7 @@
         <v>46192</v>
       </c>
       <c r="U167" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>46207</v>
       </c>
       <c r="U168" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -23668,7 +23668,7 @@
         <v>46192</v>
       </c>
       <c r="U169" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>46207</v>
       </c>
       <c r="U170" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         <v>46192</v>
       </c>
       <c r="U171" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -24067,7 +24067,7 @@
         <v>46192</v>
       </c>
       <c r="U172" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
         <v>46192</v>
       </c>
       <c r="U173" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -24333,7 +24333,7 @@
         <v>46192</v>
       </c>
       <c r="U174" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -24466,7 +24466,7 @@
         <v>46192</v>
       </c>
       <c r="U175" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>46207</v>
       </c>
       <c r="U176" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>46207</v>
       </c>
       <c r="U177" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -24865,7 +24865,7 @@
         <v>46207</v>
       </c>
       <c r="U178" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -24998,7 +24998,7 @@
         <v>46193</v>
       </c>
       <c r="U179" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>46208</v>
       </c>
       <c r="U180" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -25264,7 +25264,7 @@
         <v>46193</v>
       </c>
       <c r="U181" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V181" t="n">
         <v>0</v>
@@ -25397,7 +25397,7 @@
         <v>46193</v>
       </c>
       <c r="U182" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V182" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
         <v>46193</v>
       </c>
       <c r="U183" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V183" t="n">
         <v>0</v>
@@ -25663,7 +25663,7 @@
         <v>46208</v>
       </c>
       <c r="U184" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>46193</v>
       </c>
       <c r="U185" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V185" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         <v>46208</v>
       </c>
       <c r="U186" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V186" t="n">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>46208</v>
       </c>
       <c r="U187" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V187" t="n">
         <v>0</v>
@@ -26195,7 +26195,7 @@
         <v>46208</v>
       </c>
       <c r="U188" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V188" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
         <v>46208</v>
       </c>
       <c r="U189" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V189" t="n">
         <v>0</v>
@@ -26461,7 +26461,7 @@
         <v>46193</v>
       </c>
       <c r="U190" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V190" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>46193</v>
       </c>
       <c r="U191" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V191" t="n">
         <v>0</v>
